--- a/.qoder/output/aiAutoTester/水文数据展示/06_testcase_export/水文数据展示_测试用例_20260818_v2.xlsx
+++ b/.qoder/output/aiAutoTester/水文数据展示/06_testcase_export/水文数据展示_测试用例_20260818_v2.xlsx
@@ -4,15 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="1"/>
+    <workbookView windowWidth="22185" windowHeight="9015" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="统计汇总" sheetId="1" r:id="rId1"/>
     <sheet name="水文数据展示" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">水文数据展示!$A$1:$N$51</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -31,1117 +28,1397 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="743" uniqueCount="320">
-  <si>
-    <t>项目</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="774" uniqueCount="382">
+  <si>
+    <t>项目名称</t>
   </si>
   <si>
     <t>水文数据展示</t>
   </si>
   <si>
+    <t>生成日期</t>
+  </si>
+  <si>
+    <t>2026-08-18</t>
+  </si>
+  <si>
+    <t>生成工具</t>
+  </si>
+  <si>
+    <t>aiAutoTester 技能（优化后流水线）</t>
+  </si>
+  <si>
     <t>总用例数</t>
   </si>
   <si>
+    <t>P0占比</t>
+  </si>
+  <si>
+    <t>19.2%</t>
+  </si>
+  <si>
+    <t>按优先级统计</t>
+  </si>
+  <si>
+    <t>P0-重要紧急</t>
+  </si>
+  <si>
+    <t>P1-重要不紧急</t>
+  </si>
+  <si>
+    <t>P2-紧急不重要</t>
+  </si>
+  <si>
+    <t>按测试类型统计</t>
+  </si>
+  <si>
+    <t>功能测试</t>
+  </si>
+  <si>
+    <t>边界测试</t>
+  </si>
+  <si>
+    <t>数据测试</t>
+  </si>
+  <si>
+    <t>UI测试</t>
+  </si>
+  <si>
+    <t>异常测试</t>
+  </si>
+  <si>
+    <t>安全测试</t>
+  </si>
+  <si>
+    <t>按需求统计</t>
+  </si>
+  <si>
+    <t>新增水文数据展示页面</t>
+  </si>
+  <si>
+    <t>Tab页签切换功能</t>
+  </si>
+  <si>
+    <t>筛选区条件查询功能</t>
+  </si>
+  <si>
+    <t>河名随省份和流域级联联动</t>
+  </si>
+  <si>
+    <t>表格表头排序功能</t>
+  </si>
+  <si>
+    <t>表格分页及每页条数切换功能</t>
+  </si>
+  <si>
+    <t>近七日水位变化缩略图展示</t>
+  </si>
+  <si>
+    <t>点击缩略图弹出水位趋势弹窗</t>
+  </si>
+  <si>
+    <t>点击站名弹出同河流站点列表</t>
+  </si>
+  <si>
+    <t>超警戒水位红色高亮与延迟标签</t>
+  </si>
+  <si>
+    <t>数据导出功能</t>
+  </si>
+  <si>
+    <t>需求ID</t>
+  </si>
+  <si>
+    <t>需求名称</t>
+  </si>
+  <si>
+    <t>用例ID</t>
+  </si>
+  <si>
+    <t>用例名称</t>
+  </si>
+  <si>
+    <t>优先级</t>
+  </si>
+  <si>
+    <t>测试类型</t>
+  </si>
+  <si>
+    <t>前置条件</t>
+  </si>
+  <si>
+    <t>测试步骤</t>
+  </si>
+  <si>
+    <t>预期结果</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>标签</t>
+  </si>
+  <si>
+    <t>维护人</t>
+  </si>
+  <si>
+    <t>测试数据</t>
+  </si>
+  <si>
+    <t>评审状态</t>
+  </si>
+  <si>
+    <t>REQ-CH1-001</t>
+  </si>
+  <si>
+    <t>TP-CH1-001-001</t>
+  </si>
+  <si>
+    <t>验证水文数据展示页面加载后默认展示河道水情Tab及三个页签</t>
+  </si>
+  <si>
+    <t>用户已登录系统、水文数据模块已部署上线</t>
+  </si>
+  <si>
+    <t>1. 在系统主菜单点击「水文数据」菜单项
+2. 等待页面加载完成，查看页面顶部标题文字
+3. 查看Tab导航栏上显示的页签名称及顺序
+4. 查看当前选中的Tab页签及其高亮样式</t>
+  </si>
+  <si>
+    <t>页面顶部标题显示'水文数据'四个字
+Tab导航栏从左到右依次显示'河道水情'、'水库水情'、'实时雨情'三个页签
+'河道水情'Tab处于选中状态，页签下方显示绿色下划线高亮
+页面下方展示河道水情的筛选区与数据表格，无空白页或加载失败提示</t>
+  </si>
+  <si>
+    <t>结合截图验证页面整体布局</t>
+  </si>
+  <si>
+    <t>AI用例</t>
+  </si>
+  <si>
+    <t>李房房-38926763</t>
+  </si>
+  <si>
+    <t>进入路径: 主菜单 &gt; 水文数据</t>
+  </si>
+  <si>
+    <t>未评审</t>
+  </si>
+  <si>
+    <t>TP-CH1-001-002</t>
+  </si>
+  <si>
+    <t>验证水文数据展示页面布局与UI元素与需求截图一致</t>
+  </si>
+  <si>
+    <t>用户已登录并进入水文数据展示页面</t>
+  </si>
+  <si>
+    <t>1. 进入「水文数据」页面并停留在「河道水情」Tab
+2. 查看页面整体布局：标题、Tab栏、筛选区、表格、分页器的上下位置关系
+3. 将当前页面截图与需求文档截图逐区域对比</t>
+  </si>
+  <si>
+    <t>标题、Tab导航栏、筛选区、表格、分页器从上到下排列，与截图布局一致
+筛选区控件顺序为：日期、省份、流域、河名、站名关键字输入框、「查询」「重置」「导出」按钮，与截图一致
+表格列头顺序为：时间、行政区划、站名、水位、警戒水位、汛限水位、超警戒、来水量、当日雨情、近七日水位变化，与截图一致</t>
+  </si>
+  <si>
+    <t>UIT测试，以需求截图为对比基准</t>
+  </si>
+  <si>
+    <t>对比基准: 需求文档截图</t>
+  </si>
+  <si>
+    <t>REQ-CH1-002</t>
+  </si>
+  <si>
+    <t>TP-CH1-002-001</t>
+  </si>
+  <si>
+    <t>验证点击水库水情Tab切换后表格列头更新为水库水情字段</t>
+  </si>
+  <si>
+    <t>用户已进入水文数据展示页面、当前处于河道水情Tab</t>
+  </si>
+  <si>
+    <t>1. 点击「水库水情」Tab页签
+2. 查看该Tab页签下方是否出现绿色下划线高亮
+3. 查看表格列头是否更新为水库水情对应字段
+4. 查看表格数据行是否加载水库水情数据</t>
+  </si>
+  <si>
+    <t>'水库水情'Tab下方出现绿色下划线高亮，'河道水情'Tab高亮消失
+表格列头包含'库名'、'库水位'、'日变幅'等水库水情字段
+表格数据行显示水库水情数据，不再显示河道水情的站名数据
+最右列仍显示「近七日水位变化」缩略图列</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>按优先级统计</t>
-  </si>
-  <si>
-    <t>P0-重要紧急</t>
-  </si>
-  <si>
-    <t>P1-重要不紧急</t>
-  </si>
-  <si>
-    <t>P2-紧急不重要</t>
-  </si>
-  <si>
-    <t>P3-不紧急不重要</t>
-  </si>
-  <si>
-    <t>按测试类型统计</t>
-  </si>
-  <si>
-    <t>功能测试(FT)</t>
-  </si>
-  <si>
-    <t>边界测试(BT)</t>
-  </si>
-  <si>
-    <t>异常测试(ET)</t>
-  </si>
-  <si>
-    <t>UI测试(UIT)</t>
-  </si>
-  <si>
-    <t>数据测试(DT)</t>
-  </si>
-  <si>
-    <t>按章节统计</t>
-  </si>
-  <si>
-    <t>第1章-水文数据展示</t>
-  </si>
-  <si>
-    <t>生成日期</t>
-  </si>
-  <si>
-    <t>2026-08-18</t>
-  </si>
-  <si>
-    <t>需求ID</t>
-  </si>
-  <si>
-    <t>需求名称</t>
-  </si>
-  <si>
-    <t>用例ID</t>
-  </si>
-  <si>
-    <t>用例名称</t>
-  </si>
-  <si>
-    <t>优先级</t>
-  </si>
-  <si>
-    <t>测试类型</t>
-  </si>
-  <si>
-    <t>前置条件</t>
-  </si>
-  <si>
-    <t>测试步骤</t>
-  </si>
-  <si>
-    <t>预期结果</t>
-  </si>
-  <si>
-    <t>备注</t>
-  </si>
-  <si>
-    <t>标签</t>
-  </si>
-  <si>
-    <t>维护人</t>
-  </si>
-  <si>
-    <t>测试数据</t>
-  </si>
-  <si>
-    <t>评审状态</t>
-  </si>
-  <si>
-    <t>REQ-CH1-001</t>
-  </si>
-  <si>
-    <t>新增水文数据展示页面</t>
-  </si>
-  <si>
-    <t>TP-CH1-001-001</t>
-  </si>
-  <si>
-    <t>验证水文数据展示页面加载功能正常显示页面标题</t>
-  </si>
-  <si>
-    <t>功能测试</t>
-  </si>
-  <si>
-    <t>用户已登录系统、用户已进入水文数据模块</t>
-  </si>
-  <si>
-    <t>1. 登录系统
-2. 进入水文数据模块
-3. 观察页面加载状态</t>
-  </si>
-  <si>
-    <t>页面正常加载无报错
-页面顶部标题显示'水文数据'</t>
-  </si>
-  <si>
-    <t>P0冒烟测试：页面可用性</t>
-  </si>
-  <si>
-    <t>AI用例</t>
-  </si>
-  <si>
-    <t>李房房-38926763</t>
-  </si>
-  <si>
-    <t>已评审</t>
-  </si>
-  <si>
-    <t>TP-CH1-001-002</t>
-  </si>
-  <si>
-    <t>验证水文数据展示页面功能三个Tab页签均正常显示</t>
-  </si>
-  <si>
-    <t>水文数据展示页面已加载</t>
-  </si>
-  <si>
-    <t>1. 进入水文数据展示页面
-2. 观察Tab导航栏</t>
-  </si>
-  <si>
-    <t>Tab导航栏显示三个页签：河道水情、水库水情、实时雨情
-三个Tab页签文字清晰可读</t>
-  </si>
-  <si>
-    <t>TP-CH1-001-003</t>
-  </si>
-  <si>
-    <t>验证水文数据展示页面功能默认选中河道水情Tab</t>
-  </si>
-  <si>
-    <t>1. 进入水文数据展示页面
-2. 观察默认选中的Tab</t>
-  </si>
-  <si>
-    <t>河道水情Tab为默认选中状态
-河道水情Tab有绿色下划线高亮标识
-表格显示河道水情数据</t>
-  </si>
-  <si>
-    <t>REQ-CH1-002</t>
-  </si>
-  <si>
-    <t>Tab页签切换功能</t>
-  </si>
-  <si>
-    <t>TP-CH1-002-001</t>
-  </si>
-  <si>
-    <t>验证水文数据展示页面功能点击水库水情Tab切换显示正确</t>
-  </si>
-  <si>
-    <t>水文数据展示页面已加载，默认在河道水情Tab</t>
-  </si>
-  <si>
-    <t>1. 点击'水库水情'Tab
-2. 观察页面内容变化</t>
-  </si>
-  <si>
-    <t>页面内容切换为水库水情数据表格
-水库水情Tab显示高亮标识
-筛选区内容适配水库水情</t>
-  </si>
-  <si>
-    <t>P0冒烟测试：核心功能</t>
+    <t>切换路径: 河道水情 &gt; 水库水情</t>
   </si>
   <si>
     <t>TP-CH1-002-002</t>
   </si>
   <si>
-    <t>验证水文数据展示页面功能点击实时雨情Tab切换显示正确</t>
-  </si>
-  <si>
-    <t>1. 点击'实时雨情'Tab
-2. 观察页面内容变化</t>
-  </si>
-  <si>
-    <t>页面内容切换为实时雨情数据
-实时雨情Tab显示高亮标识</t>
-  </si>
-  <si>
-    <t>评审调整：P0降为P1，控制P0比例</t>
+    <t>验证实时雨情Tab切换后展示雨情数据表格</t>
+  </si>
+  <si>
+    <t>用户已进入水文数据展示页面</t>
+  </si>
+  <si>
+    <t>1. 点击「实时雨情」Tab页签
+2. 查看表格列头是否为雨情相关字段
+3. 查看表格数据是否为实时雨情数据</t>
+  </si>
+  <si>
+    <t>'实时雨情'Tab处于选中状态并显示绿色下划线高亮
+表格列头更新为实时雨情对应字段，不残留河道水情的'水位''警戒水位'等列
+表格加载实时雨情数据，无河道水情/水库水情的残留数据</t>
+  </si>
+  <si>
+    <t>实时雨情具体列定义需求未明确，执行前需与需求方确认列清单</t>
   </si>
   <si>
     <t>TP-CH1-002-003</t>
   </si>
   <si>
-    <t>验证水文数据展示页面功能当前选中Tab有高亮样式标识</t>
-  </si>
-  <si>
-    <t>UI测试</t>
-  </si>
-  <si>
-    <t>1. 观察当前选中Tab的样式
-2. 切换到其他Tab
-3. 观察高亮标识是否跟随切换</t>
-  </si>
-  <si>
-    <t>当前选中Tab有绿色下划线高亮
-切换Tab后高亮标识跟随到新Tab
-未选中Tab无高亮样式</t>
-  </si>
-  <si>
-    <t>UI测试：基于截图验证高亮样式</t>
-  </si>
-  <si>
-    <t>TP-CH1-002-004</t>
-  </si>
-  <si>
-    <t>验证水文数据展示页面功能快速多次切换Tab页面响应正确</t>
-  </si>
-  <si>
-    <t>异常测试</t>
-  </si>
-  <si>
-    <t>1. 快速连续点击不同Tab（河道水情→水库水情→实时雨情→河道水情）
-2. 观察最终页面状态</t>
-  </si>
-  <si>
-    <t>最终显示最后一次点击的Tab内容
-页面无报错或卡顿
-数据加载正确</t>
-  </si>
-  <si>
-    <t>异常测试：快速切换场景</t>
+    <t>验证三个Tab快速来回切换时页面内容均与所选Tab一致</t>
+  </si>
+  <si>
+    <t>1. 依次点击「河道水情」→「水库水情」→「实时雨情」→「河道水情」Tab
+2. 每次切换后查看当前高亮Tab名称
+3. 每次切换后查看表格列头与数据内容是否对应</t>
+  </si>
+  <si>
+    <t>每次切换后仅当前Tab显示绿色下划线高亮，其余Tab无高亮
+每次切换后表格列头与当前Tab类型一一对应
+最终停留在'河道水情'Tab，表格恢复显示河道水情数据（如杨庄站水位58.06m）</t>
+  </si>
+  <si>
+    <t>切换序列: 河道水情→水库水情→实时雨情→河道水情</t>
   </si>
   <si>
     <t>REQ-CH1-003</t>
   </si>
   <si>
-    <t>筛选区条件查询功能</t>
-  </si>
-  <si>
     <t>TP-CH1-003-001</t>
   </si>
   <si>
-    <t>验证水文数据筛选区功能点击查询按钮后数据按条件正确过滤</t>
-  </si>
-  <si>
-    <t>水文数据展示页面已加载、表格中有数据</t>
-  </si>
-  <si>
-    <t>1. 选择省份为'河南'
-2. 点击'查询'按钮
-3. 观察表格数据</t>
-  </si>
-  <si>
-    <t>表格仅显示河南省的数据
-表格数据正确刷新</t>
-  </si>
-  <si>
-    <t>P0冒烟测试：核心查询功能</t>
+    <t>验证日期+省份+流域+河名组合条件查询后表格数据全部匹配筛选条件</t>
+  </si>
+  <si>
+    <t>用户已进入河道水情Tab、系统存在2026-08-15河南省黄河数据</t>
+  </si>
+  <si>
+    <t>1. 在「日期」选择器选择'2026-08-15'
+2. 在「省份」下拉框选择'河南'
+3. 在「流域」下拉框选择'黄河流域'
+4. 在「河名」下拉框选择'黄河'
+5. 点击「查询」按钮
+6. 逐行查看表格'时间'、'行政区划'列的值</t>
+  </si>
+  <si>
+    <t>表格所有数据行的'时间'列均为'2026-08-15'
+表格所有数据行的'行政区划'列均为'河南'
+表格显示的站点（如杨庄、小浪底、花园口）均属于黄河流域黄河水系
+分页器总条数与查询结果条数一致（截图场景为10条）</t>
+  </si>
+  <si>
+    <t>对应截图默认查询场景</t>
+  </si>
+  <si>
+    <t>日期=2026-08-15; 省份=河南; 流域=黄河流域; 河名=黄河</t>
+  </si>
+  <si>
+    <t>TP-CH1-003-002</t>
+  </si>
+  <si>
+    <t>验证站名关键字'杨'模糊查询仅返回站名包含杨的站点</t>
+  </si>
+  <si>
+    <t>用户已进入河道水情Tab、系统存在站名'杨庄'的数据</t>
+  </si>
+  <si>
+    <t>1. 在「站名关键字」输入框输入'杨'
+2. 点击「查询」按钮
+3. 逐行查看表格'站名'列的值
+4. 查看分页器显示的总条数</t>
+  </si>
+  <si>
+    <t>表格所有数据行的'站名'列均包含字符'杨'（如'杨庄'）
+不包含'小浪底'、'花园口'等站名不含'杨'的站点
+分页器总条数等于符合条件的站点数量
+'杨庄'行水位显示58.06，与全量查询时该站数值一致</t>
+  </si>
+  <si>
+    <t>站名关键字=杨</t>
+  </si>
+  <si>
+    <t>TP-CH1-003-003</t>
+  </si>
+  <si>
+    <t>验证点击重置按钮后所有筛选控件恢复默认值</t>
+  </si>
+  <si>
+    <t>用户已设置日期=2026-08-15、省份=河南、流域=黄河流域、河名=黄河、站名关键字=杨</t>
+  </si>
+  <si>
+    <t>1. 确认筛选区五个控件均已填入上述值
+2. 点击「重置」按钮
+3. 逐一查看日期、省份、流域、河名、站名关键字五个控件的当前值</t>
+  </si>
+  <si>
+    <t>「日期」选择器恢复为系统默认日期
+「省份」「流域」「河名」三个下拉框均恢复为占位文案'请选择'
+「站名关键字」输入框清空，恢复占位文案'输入站名关键字'
+「重置」按钮点击后不触发自动查询，表格数据保持重置前状态直至下次查询</t>
+  </si>
+  <si>
+    <t>TP-CH1-003-004</t>
+  </si>
+  <si>
+    <t>验证日期选择未来日期'2026-08-19'查询后表格显示暂无数据</t>
+  </si>
+  <si>
+    <t>当前系统日期为2026-08-18、用户已进入河道水情Tab</t>
+  </si>
+  <si>
+    <t>1. 在「日期」选择器选择'2026-08-19'（晚于当前日期1天）
+2. 点击「查询」按钮
+3. 查看表格数据区域与分页器总条数显示</t>
+  </si>
+  <si>
+    <t>表格数据区域显示'暂无数据'空状态提示
+分页器总条数显示为0
+页面无JS报错弹窗或接口异常提示</t>
+  </si>
+  <si>
+    <t>上边界：超出当前日期的日期</t>
+  </si>
+  <si>
+    <t>日期=2026-08-19(未来日期)</t>
+  </si>
+  <si>
+    <t>TP-CH1-003-005</t>
+  </si>
+  <si>
+    <t>验证仅选择省份'河南'不选其他条件时查询返回该省全部站点</t>
+  </si>
+  <si>
+    <t>用户已进入河道水情Tab</t>
+  </si>
+  <si>
+    <t>1. 点击「重置」按钮清空所有筛选条件
+2. 仅在「省份」下拉框选择'河南'，其余条件保持不选
+3. 点击「查询」按钮
+4. 逐行查看表格'行政区划'列的值</t>
+  </si>
+  <si>
+    <t>表格所有数据行的'行政区划'列均为'河南'
+结果包含河南省下所有流域、所有河流的站点，不限于黄河
+页面无接口报错或空指针异常</t>
+  </si>
+  <si>
+    <t>省份=河南; 其余条件=空</t>
+  </si>
+  <si>
+    <t>TP-CH1-003-006</t>
+  </si>
+  <si>
+    <t>验证1秒内快速连点查询按钮5次仅执行一次查询且无重复数据</t>
+  </si>
+  <si>
+    <t>用户已进入河道水情Tab、浏览器开发者工具已打开Network面板</t>
+  </si>
+  <si>
+    <t>1. 设置筛选条件：日期=2026-08-15、省份=河南
+2. 在1秒内快速连续点击「查询」按钮5次
+3. 在Network面板统计列表查询接口的请求次数
+4. 查看表格是否存在重复数据行</t>
+  </si>
+  <si>
+    <t>列表查询接口最终仅以最后一次请求的结果渲染表格（防抖或请求取消机制生效）
+表格无重复站名行（如'杨庄'仅出现1次）
+页面无并发响应错乱导致的数据闪烁或报错</t>
+  </si>
+  <si>
+    <t>防重复提交场景</t>
+  </si>
+  <si>
+    <t>连点次数=5; 间隔&lt;200ms</t>
+  </si>
+  <si>
+    <t>REQ-CH1-004</t>
+  </si>
+  <si>
+    <t>TP-CH1-004-001</t>
+  </si>
+  <si>
+    <t>验证选择省份河南后流域下拉框联动加载黄河流域淮河等选项</t>
+  </si>
+  <si>
+    <t>用户已进入河道水情Tab、筛选区所有控件为空</t>
+  </si>
+  <si>
+    <t>1. 在「省份」下拉框选择'河南'
+2. 点击展开「流域」下拉框
+3. 查看流域选项列表内容
+4. 查看「河名」下拉框在尚未选择流域时的状态</t>
+  </si>
+  <si>
+    <t>「流域」下拉框选项更新为河南省涉及的流域（含'黄河流域'）
+流域选项中不包含与河南无关的流域
+「河名」下拉框在选择流域前无可选项或保持禁用状态
+省份切换过程无接口报错</t>
   </si>
   <si>
     <t>省份=河南</t>
   </si>
   <si>
-    <t>TP-CH1-003-002</t>
-  </si>
-  <si>
-    <t>验证水文数据筛选区功能日期选择器可正常选择日期范围</t>
-  </si>
-  <si>
-    <t>1. 点击日期选择器
-2. 选择起始日期和结束日期
-3. 点击查询</t>
-  </si>
-  <si>
-    <t>日期选择器弹出日期面板
-可选择日期范围
-查询后数据按日期范围过滤</t>
-  </si>
-  <si>
-    <t>日期范围=2026/07/25-2026/07/29</t>
-  </si>
-  <si>
-    <t>TP-CH1-003-003</t>
-  </si>
-  <si>
-    <t>验证水文数据筛选区功能省份和流域下拉框默认值及选择功能正常</t>
-  </si>
-  <si>
-    <t>1. 观察省份下拉框默认值
-2. 观察流域下拉框默认值
-3. 分别选择不同省份和流域</t>
-  </si>
-  <si>
-    <t>省份下拉框默认显示'全部'
-流域下拉框默认显示'全部'
-可选择具体省份和流域</t>
-  </si>
-  <si>
-    <t>TP-CH1-003-004</t>
-  </si>
-  <si>
-    <t>验证水文数据筛选区功能站名输入框支持关键字模糊搜索</t>
-  </si>
-  <si>
-    <t>1. 在站名输入框输入关键字'庄'
-2. 点击查询
-3. 观察结果</t>
-  </si>
-  <si>
-    <t>站名输入框可正常输入文字
-查询结果显示站名包含'庄'的数据（如杨庄、周堂桥等）</t>
-  </si>
-  <si>
-    <t>站名关键字=庄</t>
-  </si>
-  <si>
-    <t>TP-CH1-003-005</t>
-  </si>
-  <si>
-    <t>验证水文数据筛选区功能多条件组合查询结果正确</t>
-  </si>
-  <si>
-    <t>1. 选择省份='河南'
-2. 选择流域='淮河'
-3. 输入站名关键字='庄'
-4. 点击查询</t>
-  </si>
-  <si>
-    <t>表格显示同时满足三个条件的数据
-结果为河南省淮河流域站名含'庄'的记录</t>
-  </si>
-  <si>
-    <t>省份=河南; 流域=淮河; 站名关键字=庄</t>
-  </si>
-  <si>
-    <t>TP-CH1-003-006</t>
-  </si>
-  <si>
-    <t>验证水文数据筛选区功能无匹配数据时显示空状态提示</t>
-  </si>
-  <si>
-    <t>1. 输入不存在的站名'XYZTEST'
-2. 点击查询
-3. 观察表格状态</t>
-  </si>
-  <si>
-    <t>表格显示空状态提示
-提示文字友好（如'暂无数据'）</t>
-  </si>
-  <si>
-    <t>站名关键字=XYZTEST</t>
-  </si>
-  <si>
-    <t>TP-CH1-003-007</t>
-  </si>
-  <si>
-    <t>验证水文数据筛选区功能点击重置按钮后筛选条件恢复默认值</t>
-  </si>
-  <si>
-    <t>已设置多个筛选条件并执行查询</t>
-  </si>
-  <si>
-    <t>1. 设置省份、流域、河名、站名等筛选条件
-2. 点击查询确认数据已过滤
-3. 点击'重置'按钮
-4. 观察筛选区和表格</t>
-  </si>
-  <si>
-    <t>所有筛选项恢复默认值（省份=全部、流域=全部等）
-表格恢复显示全部数据</t>
-  </si>
-  <si>
-    <t>TP-CH1-003-008</t>
-  </si>
-  <si>
-    <t>验证水文数据筛选区功能点击导出按钮后当前筛选数据正确导出</t>
-  </si>
-  <si>
-    <t>水文数据展示页面已加载，表格有数据</t>
-  </si>
-  <si>
-    <t>1. 设置筛选条件（如省份=河南）
-2. 点击查询
-3. 点击'导出'按钮
-4. 检查导出的文件</t>
-  </si>
-  <si>
-    <t>导出文件成功生成
-导出文件包含当前筛选条件下的数据
-导出文件格式正确（Excel/CSV）</t>
-  </si>
-  <si>
-    <t>评审补充：截图显示有导出按钮，补充对应测试点</t>
-  </si>
-  <si>
-    <t>REQ-CH1-004</t>
-  </si>
-  <si>
-    <t>河名随省份和流域级联联动</t>
-  </si>
-  <si>
-    <t>TP-CH1-004-001</t>
-  </si>
-  <si>
-    <t>验证水文数据筛选区功能选择省份后河名列表正确过滤</t>
-  </si>
-  <si>
-    <t>1. 选择省份='河南'
-2. 点击河名下拉框
-3. 观察可选河流列表</t>
-  </si>
-  <si>
-    <t>河名列表仅显示河南省的河流
-不显示其他省份的河流</t>
-  </si>
-  <si>
     <t>TP-CH1-004-002</t>
   </si>
   <si>
-    <t>验证水文数据筛选区功能省份和流域组合后河名列表为交集过滤</t>
-  </si>
-  <si>
-    <t>1. 选择省份='河南'
-2. 选择流域='淮河'
-3. 点击河名下拉框
-4. 观察可选河流列表</t>
-  </si>
-  <si>
-    <t>河名列表仅显示河南省淮河流域的河流（如洪河、汝河等）
-不显示非淮河流域的河南河流</t>
-  </si>
-  <si>
-    <t>省份=河南; 流域=淮河</t>
+    <t>验证清空省份后流域和河名选项同步清空并恢复禁用</t>
+  </si>
+  <si>
+    <t>已选择省份=河南、流域=黄河流域、河名=黄河</t>
+  </si>
+  <si>
+    <t>1. 点击「省份」下拉框的清除图标（或选择空选项）清空省份
+2. 查看「流域」下拉框的当前值与可选项
+3. 查看「河名」下拉框的当前值与可选项</t>
+  </si>
+  <si>
+    <t>「流域」下拉框已选值被清空，恢复占位文案'请选择'
+「河名」下拉框已选值被清空，恢复占位文案'请选择'
+「流域」「河名」下拉框无可选项或处于禁用状态
+不残留'黄河流域'、'黄河'等旧选项</t>
   </si>
   <si>
     <t>TP-CH1-004-003</t>
   </si>
   <si>
-    <t>验证水文数据筛选区功能取消省份选择后河名列表恢复全部</t>
-  </si>
-  <si>
-    <t>已选择省份='河南'，河名已过滤</t>
-  </si>
-  <si>
-    <t>1. 将省份改回'全部'
-2. 点击河名下拉框
-3. 观察可选河流列表</t>
-  </si>
-  <si>
-    <t>河名列表恢复显示所有河流
-不再受省份限制</t>
+    <t>验证选择河南+黄河流域后河名下拉框联动加载黄河选项</t>
+  </si>
+  <si>
+    <t>筛选区所有控件为空、用户已进入河道水情Tab</t>
+  </si>
+  <si>
+    <t>1. 在「省份」下拉框选择'河南'
+2. 在「流域」下拉框选择'黄河流域'
+3. 点击展开「河名」下拉框
+4. 查看河名选项列表内容</t>
+  </si>
+  <si>
+    <t>「河名」下拉框选项更新为河南省黄河流域下的河流（含'黄河'）
+河名选项中不包含其他流域或其他省份的河流
+选择'黄河'后「河名」下拉框显示已选值'黄河'，点击「查询」可返回黄河水系站点数据</t>
+  </si>
+  <si>
+    <t>截图显示河名已联动出'黄河'</t>
+  </si>
+  <si>
+    <t>省份=河南; 流域=黄河流域</t>
   </si>
   <si>
     <t>TP-CH1-004-004</t>
   </si>
   <si>
-    <t>验证水文数据筛选区功能河名联动不影响已选的其他筛选项</t>
-  </si>
-  <si>
-    <t>已设置日期和站名筛选条件</t>
-  </si>
-  <si>
-    <t>1. 设置日期范围
-2. 输入站名关键字
-3. 切换省份选择
-4. 观察日期和站名是否保持</t>
-  </si>
-  <si>
-    <t>日期和站名筛选条件保持不变
-仅河名列表更新</t>
+    <t>验证无河流数据的省份+流域组合下河名下拉框显示空选项状态</t>
+  </si>
+  <si>
+    <t>系统存在某省份+流域组合无河流数据（由测试数据准备确认）</t>
+  </si>
+  <si>
+    <t>1. 在「省份」下拉框选择该无河流数据的省份
+2. 在「流域」下拉框选择对应流域
+3. 点击展开「河名」下拉框
+4. 查看下拉框展示内容</t>
+  </si>
+  <si>
+    <t>「河名」下拉框展开后显示'暂无数据'或空选项提示
+不显示其他省份/流域的河流选项
+页面无接口报错或渲染异常</t>
+  </si>
+  <si>
+    <t>空值边界场景</t>
+  </si>
+  <si>
+    <t>省份+流域组合=无河流数据的组合</t>
   </si>
   <si>
     <t>REQ-CH1-005</t>
   </si>
   <si>
-    <t>表格表头排序功能</t>
-  </si>
-  <si>
     <t>TP-CH1-005-001</t>
   </si>
   <si>
-    <t>验证水文数据表格功能点击表头首次排序为升序排列</t>
-  </si>
-  <si>
-    <t>表格中有数据</t>
-  </si>
-  <si>
-    <t>1. 点击'水位(米)'列表头
-2. 观察数据排列顺序</t>
-  </si>
-  <si>
-    <t>表格数据按水位升序排列
-表头显示升序排序图标</t>
+    <t>验证点击水位表头升序排序后数值从小到大排列并显示升序图标</t>
+  </si>
+  <si>
+    <t>已查询出河南黄河10条数据、表格未处于排序状态</t>
+  </si>
+  <si>
+    <t>1. 查看排序前'水位'列各行的值
+2. 点击「水位」列表头一次
+3. 逐行查看'水位'列数值排列顺序
+4. 查看「水位」列表头旁的排序图标方向</t>
+  </si>
+  <si>
+    <t>'水位'列数值按从小到大排列：17.71(利津)→33.12(泺口)→48.61(孙口)→58.06(杨庄)→…→234.53(小浪底)
+「水位」列表头显示向上的升序箭头图标
+其余列数据随整行一起移动，行内对应关系不变（如234.53仍对应小浪底）
+分页器总条数保持10不变</t>
+  </si>
+  <si>
+    <t>截图数据值用于校验排序结果</t>
+  </si>
+  <si>
+    <t>排序列=水位; 方向=升序</t>
   </si>
   <si>
     <t>TP-CH1-005-002</t>
   </si>
   <si>
-    <t>验证水文数据表格功能再次点击同一表头切换为降序排列</t>
-  </si>
-  <si>
-    <t>已对某列执行升序排序</t>
-  </si>
-  <si>
-    <t>1. 再次点击'水位(米)'列表头
-2. 观察数据排列顺序</t>
-  </si>
-  <si>
-    <t>表格数据按水位降序排列
-表头显示降序排序图标</t>
+    <t>验证再次点击水位表头切换为降序且图标方向同步切换</t>
+  </si>
+  <si>
+    <t>已执行水位列升序排序</t>
+  </si>
+  <si>
+    <t>1. 再次点击「水位」列表头
+2. 逐行查看'水位'列数值排列顺序
+3. 查看表头排序图标方向</t>
+  </si>
+  <si>
+    <t>'水位'列数值按从大到小排列：234.53(小浪底)→225.30(龙羊峡)→90.69(花园口)→…→17.71(利津)
+「水位」列表头排序图标切换为向下的降序箭头
+行内数据对应关系保持不变</t>
+  </si>
+  <si>
+    <t>排序列=水位; 方向=降序</t>
   </si>
   <si>
     <t>TP-CH1-005-003</t>
   </si>
   <si>
-    <t>验证水文数据表格功能第三次点击表头取消排序恢复默认顺序</t>
-  </si>
-  <si>
-    <t>已对某列执行降序排序</t>
-  </si>
-  <si>
-    <t>1. 第三次点击'水位(米)'列表头
-2. 观察数据排列顺序</t>
-  </si>
-  <si>
-    <t>表格恢复默认排序
-排序图标消失或恢复初始状态</t>
+    <t>验证超警戒列按数值排序且负值排序符合数学规则</t>
+  </si>
+  <si>
+    <t>已查询出河南黄河10条数据、超警戒列含负值（如-91.94）</t>
+  </si>
+  <si>
+    <t>1. 点击「超警戒」列表头进行升序排序
+2. 逐行查看'超警戒'列数值顺序
+3. 核对首行与末行的站名和数值</t>
+  </si>
+  <si>
+    <t>'超警戒'列按数值升序排列：-91.94(杨庄)排第一行
+0.30(龙羊峡)排最后一行，为唯一正值
+负值之间按绝对值从大到小排列（-91.94→-72.82→-29.47→…→-2.91）</t>
+  </si>
+  <si>
+    <t>排序列=超警戒; 含负值数据</t>
   </si>
   <si>
     <t>TP-CH1-005-004</t>
   </si>
   <si>
-    <t>验证水文数据表格功能排序图标状态与当前排序方向一致</t>
-  </si>
-  <si>
-    <t>1. 点击列头升序排序，观察图标
-2. 再次点击降序排序，观察图标变化</t>
-  </si>
-  <si>
-    <t>升序时图标箭头向上
-降序时图标箭头向下
-未排序时图标为灰色或无箭头</t>
-  </si>
-  <si>
-    <t>UI测试：基于截图验证排序图标</t>
+    <t>验证来水量列含--缺失值时排序不报错且缺失值排列位置稳定</t>
+  </si>
+  <si>
+    <t>表格'来水量'列存在'--'缺失值（截图显示全部为--）</t>
+  </si>
+  <si>
+    <t>1. 点击「来水量」列表头进行升序排序
+2. 查看表格渲染状态与控制台是否有报错
+3. 再次点击切换降序，查看'--'值的排列位置</t>
+  </si>
+  <si>
+    <t>排序操作不触发页面报错或白屏
+全部为'--'时表格保持原有行序或统一排在固定位置
+'--'缺失值在升序与降序下排列位置规则一致（统一置顶或统一置底）</t>
+  </si>
+  <si>
+    <t>排序列=来水量; 缺失值=--</t>
   </si>
   <si>
     <t>TP-CH1-005-005</t>
   </si>
   <si>
-    <t>验证水文数据表格功能排序后分页数据正确显示</t>
-  </si>
-  <si>
-    <t>数据量超过一页</t>
-  </si>
-  <si>
-    <t>1. 对某列升序排序
-2. 翻到第二页
-3. 观察数据是否继续升序</t>
-  </si>
-  <si>
-    <t>第二页数据继续按升序排列
-分页数据与排序逻辑一致</t>
+    <t>验证水位列排序后翻页再返回当前页排序顺序保持不变</t>
+  </si>
+  <si>
+    <t>数据量超过每页条数（每页条数切换为5条，共10条数据）、已执行水位列升序排序</t>
+  </si>
+  <si>
+    <t>1. 将每页条数切换为'5条/页'
+2. 点击「水位」列表头执行升序排序
+3. 点击分页器「2」翻到第2页
+4. 点击分页器「1」返回第1页，查看'水位'列顺序</t>
+  </si>
+  <si>
+    <t>第2页水位值均大于第1页最大值，全局升序关系保持
+返回第1页后水位列仍为17.71、33.12、48.61、58.06、63.31升序
+表头升序图标在翻页过程中持续显示</t>
+  </si>
+  <si>
+    <t>每页条数=5; 排序列=水位</t>
   </si>
   <si>
     <t>REQ-CH1-006</t>
   </si>
   <si>
-    <t>表格分页及每页条数切换功能</t>
-  </si>
-  <si>
     <t>TP-CH1-006-001</t>
   </si>
   <si>
-    <t>验证水文数据表格功能分页控件正常显示总页数和当前页</t>
-  </si>
-  <si>
-    <t>数据量超过一页显示数量</t>
-  </si>
-  <si>
-    <t>1. 观察表格底部分页控件
-2. 查看总页数和当前页显示</t>
-  </si>
-  <si>
-    <t>分页控件显示总页数
-当前页高亮显示
-可点击不同页码</t>
+    <t>验证分页器默认显示20条每页且总条数为10</t>
+  </si>
+  <si>
+    <t>已查询出河南黄河10条数据</t>
+  </si>
+  <si>
+    <t>1. 查看表格下方分页器左侧文字
+2. 查看每页条数下拉框的默认值
+3. 统计表格当前渲染的数据行数</t>
+  </si>
+  <si>
+    <t>分页器左侧显示'共 10'（总条数为10）
+每页条数下拉框默认显示'20条/页'
+表格渲染数据行数为10行（小于每页条数时全部展示）</t>
+  </si>
+  <si>
+    <t>对应截图分页器状态</t>
+  </si>
+  <si>
+    <t>总条数=10; 默认每页=20</t>
   </si>
   <si>
     <t>TP-CH1-006-002</t>
   </si>
   <si>
-    <t>验证水文数据表格功能切换每页显示条数后数据正确刷新</t>
-  </si>
-  <si>
-    <t>表格中有足够数据</t>
-  </si>
-  <si>
-    <t>1. 将每页条数从10切换为20
-2. 观察表格数据行数
-3. 切换为50
-4. 观察表格数据行数</t>
-  </si>
-  <si>
-    <t>切换为20条后显示20行数据
-切换为50条后显示50行数据
-数据内容正确</t>
-  </si>
-  <si>
-    <t>每页条数=10/20/50</t>
+    <t>验证切换每页条数为50后表格刷新且分页信息同步更新</t>
+  </si>
+  <si>
+    <t>已查询出列表数据、当前每页条数为20</t>
+  </si>
+  <si>
+    <t>1. 点击分页器中的每页条数下拉框
+2. 选择'50条/页'选项
+3. 查看表格数据行数与分页器页码显示</t>
+  </si>
+  <si>
+    <t>每页条数下拉框显示'50条/页'
+表格按50条/页重新加载数据（数据量&gt;50时显示50行）
+当前页码重置为第1页
+切换过程无接口报错</t>
+  </si>
+  <si>
+    <t>每页条数: 20→50</t>
   </si>
   <si>
     <t>TP-CH1-006-003</t>
   </si>
   <si>
-    <t>验证水文数据表格功能最后一页数据不足时正确显示剩余数据</t>
-  </si>
-  <si>
-    <t>数据量不是每页条数的整数倍</t>
-  </si>
-  <si>
-    <t>1. 翻到最后一页
-2. 观察数据行数</t>
-  </si>
-  <si>
-    <t>最后一页显示剩余数据（不足一页条数）
-页面无异常</t>
+    <t>验证数据量10条小于每页20条时仅显示一页且翻页按钮不可点击</t>
+  </si>
+  <si>
+    <t>查询结果总条数为10、每页条数为20</t>
+  </si>
+  <si>
+    <t>1. 查看分页器显示的页码数量
+2. 查看「下一页」按钮的可用状态
+3. 点击「下一页」按钮，查看表格是否变化</t>
+  </si>
+  <si>
+    <t>分页器仅显示页码'1'，无第2页
+「下一页」按钮为置灰禁用状态
+点击置灰的「下一页」按钮无任何响应，表格数据不变</t>
+  </si>
+  <si>
+    <t>下边界：数据量不足一页</t>
+  </si>
+  <si>
+    <t>总条数=10; 每页=20</t>
   </si>
   <si>
     <t>TP-CH1-006-004</t>
   </si>
   <si>
-    <t>验证水文数据表格功能分页与排序组合使用结果正确</t>
-  </si>
-  <si>
-    <t>1. 对水位列升序排序
-2. 切换每页条数为20
-3. 翻到第二页
-4. 验证数据连续性</t>
-  </si>
-  <si>
-    <t>排序和分页组合后数据正确
-跨页数据排序连续</t>
+    <t>验证数据超过每页条数时点击第2页加载后续数据</t>
+  </si>
+  <si>
+    <t>查询结果总条数大于20条</t>
+  </si>
+  <si>
+    <t>1. 确认分页器显示页码至少为2页
+2. 记录第1页最后一行的站名
+3. 点击分页器页码「2」
+4. 查看第2页首行数据与页码高亮状态</t>
+  </si>
+  <si>
+    <t>第2页加载的数据与第1页无重复站名
+页码'2'处于高亮选中状态
+「共 N」总条数显示保持不变</t>
+  </si>
+  <si>
+    <t>总条数&gt;20</t>
   </si>
   <si>
     <t>REQ-CH1-007</t>
   </si>
   <si>
-    <t>近七日水位变化缩略图展示</t>
-  </si>
-  <si>
     <t>TP-CH1-007-001</t>
   </si>
   <si>
-    <t>验证水文数据表格功能近七日水位变化缩略图正确展示在表格最右列</t>
-  </si>
-  <si>
-    <t>河道水情Tab已加载，表格有数据</t>
-  </si>
-  <si>
-    <t>1. 观察表格最右列
-2. 确认列标题为'近七日水位变化'
-3. 确认每行都有缩略图</t>
-  </si>
-  <si>
-    <t>最右列标题为'近七日水位变化'
-每行数据对应一个缩略图
-缩略图大小适中不影响布局</t>
-  </si>
-  <si>
-    <t>UI测试：基于截图验证缩略图位置和展示</t>
+    <t>验证河道水情表格最右列显示近七日水位变化缩略图</t>
+  </si>
+  <si>
+    <t>已查询出河道水情数据、站点存在近七日水位历史数据</t>
+  </si>
+  <si>
+    <t>1. 查看表格最右列的列头文字
+2. 查看杨庄行最右列单元格内容
+3. 查看小浪底行最右列单元格内容</t>
+  </si>
+  <si>
+    <t>表格最右列列头显示'近七日水位变化'
+每行最右列单元格渲染一个折线缩略图，非文字或空白
+缩略图横轴覆盖近7个日期，纵轴为该站水位走势</t>
+  </si>
+  <si>
+    <t>验证行: 杨庄、小浪底</t>
   </si>
   <si>
     <t>TP-CH1-007-002</t>
   </si>
   <si>
-    <t>验证水文数据表格功能水位上涨段缩略图显示为绿色线条</t>
-  </si>
-  <si>
-    <t>存在水位上涨的站点数据</t>
-  </si>
-  <si>
-    <t>1. 找到水位上涨的站点行（如庙湾、新蔡等）
-2. 观察缩略图颜色</t>
-  </si>
-  <si>
-    <t>水位上涨段显示为绿色线条</t>
-  </si>
-  <si>
-    <t>基于截图：庙湾、新蔡、方集等行缩略图为绿色（上涨）</t>
+    <t>验证缩略图上涨段显示绿色下跌段显示红色</t>
+  </si>
+  <si>
+    <t>存在近七日水位先跌后涨的站点数据（用于同时验证两种颜色）</t>
+  </si>
+  <si>
+    <t>1. 找到近七日水位存在上涨段的站点行，查看其缩略图上涨段线段颜色
+2. 查看同一缩略图中下跌段线段颜色
+3. 与需求文档中的颜色规则说明对比</t>
+  </si>
+  <si>
+    <t>水位上升的两个相邻日期之间的线段为绿色
+水位下降的两个相邻日期之间的线段为红色
+颜色规则在缩略图全宽范围内一致应用，无颜色错误段</t>
+  </si>
+  <si>
+    <t>UIT测试，颜色规则为核心验收项</t>
+  </si>
+  <si>
+    <t>验证对象: 缩略图线段颜色</t>
   </si>
   <si>
     <t>TP-CH1-007-003</t>
   </si>
   <si>
-    <t>验证水文数据表格功能水位下跌段缩略图显示为红色线条</t>
-  </si>
-  <si>
-    <t>存在水位下跌的站点数据</t>
-  </si>
-  <si>
-    <t>1. 找到水位下跌的站点行（如杨庄、五沟营等）
-2. 观察缩略图颜色</t>
-  </si>
-  <si>
-    <t>水位下跌段显示为红色线条</t>
-  </si>
-  <si>
-    <t>基于截图：杨庄、五沟营、驻马店等行缩略图为红色（下跌）</t>
+    <t>验证某日期无水位数据时缩略图对应位置留空不连线</t>
+  </si>
+  <si>
+    <t>存在近7日中某日缺测的站点数据（由测试数据准备确认）</t>
+  </si>
+  <si>
+    <t>1. 找到存在缺测日期的站点行
+2. 查看缩略图中缺测日期对应位置的展示
+3. 查看缺测日期前后两个有数据点之间的连线情况</t>
+  </si>
+  <si>
+    <t>缺测日期位置不绘制数据点，显示为留空
+缺测日期两侧的数据点之间不直接连线（或以断线方式呈现）
+缩略图整体不报错、不渲染异常折线</t>
+  </si>
+  <si>
+    <t>缺测日期: 近7日中任选1日无数据</t>
   </si>
   <si>
     <t>TP-CH1-007-004</t>
   </si>
   <si>
-    <t>验证水文数据表格功能无数据日期缩略图对应位置留空不连线</t>
-  </si>
-  <si>
-    <t>存在部分日期无水位数据的站点</t>
-  </si>
-  <si>
-    <t>1. 找到有数据缺失的站点行
-2. 观察缩略图中无数据日期的表现</t>
-  </si>
-  <si>
-    <t>无数据的日期位置留空，不绘制连线
-有数据的日期正常连线</t>
+    <t>验证水库水情表格最右列同样显示近七日水位变化缩略图</t>
+  </si>
+  <si>
+    <t>用户已切换到水库水情Tab、水库存在近七日库水位数据</t>
+  </si>
+  <si>
+    <t>1. 点击「水库水情」Tab
+2. 查看表格最右列列头文字
+3. 查看任意水库行最右列的缩略图渲染</t>
+  </si>
+  <si>
+    <t>水库水情表格最右列列头为'近七日水位变化'
+每个水库行渲染近7日库水位折线缩略图
+缩略图颜色规则与河道水情一致：上涨段绿色、下跌段红色</t>
+  </si>
+  <si>
+    <t>验证Tab: 水库水情</t>
   </si>
   <si>
     <t>TP-CH1-007-005</t>
   </si>
   <si>
-    <t>验证水文数据表格功能水库水情Tab下也展示近七日水位变化缩略图</t>
-  </si>
-  <si>
-    <t>切换到水库水情Tab</t>
-  </si>
-  <si>
-    <t>1. 切换到水库水情Tab
-2. 观察表格最右列</t>
-  </si>
-  <si>
-    <t>水库水情表格最右列也显示近七日水位变化缩略图
-颜色规则一致（上涨绿、下跌红）</t>
+    <t>验证缩略图尺寸位置与需求截图一致且不遮挡相邻列内容</t>
+  </si>
+  <si>
+    <t>已查询出河道水情数据</t>
+  </si>
+  <si>
+    <t>1. 查看缩略图在单元格内的垂直居中情况
+2. 将页面截图与需求截图对比缩略图尺寸
+3. 查看缩略图是否超出单元格边界或遮挡'当日雨情'列</t>
+  </si>
+  <si>
+    <t>缩略图在单元格内垂直居中显示
+缩略图宽高与需求截图比例一致
+缩略图不超出单元格边界，相邻列内容完整可见</t>
   </si>
   <si>
     <t>REQ-CH1-008</t>
   </si>
   <si>
-    <t>点击缩略图弹出水位趋势弹窗</t>
-  </si>
-  <si>
     <t>TP-CH1-008-001</t>
   </si>
   <si>
-    <t>验证水文数据表格功能点击缩略图弹出水位趋势详情弹窗</t>
-  </si>
-  <si>
-    <t>河道水情Tab已加载，表格有缩略图</t>
-  </si>
-  <si>
-    <t>1. 点击任意一行的近七日水位变化缩略图
-2. 观察弹窗是否弹出</t>
-  </si>
-  <si>
-    <t>弹出水位趋势详情弹窗
-弹窗包含统计指标和折线图</t>
+    <t>验证点击杨庄缩略图弹出趋势弹窗且上方显示四项统计指标</t>
+  </si>
+  <si>
+    <t>已查询出河道水情数据、杨庄站存在近7日完整水位数据</t>
+  </si>
+  <si>
+    <t>1. 找到'杨庄'行，点击其「近七日水位变化」缩略图
+2. 查看弹窗顶部展示的统计指标项及顺序
+3. 查看每项指标是否显示具体数值</t>
+  </si>
+  <si>
+    <t>点击后弹出趋势弹窗，弹窗标题含'杨庄'站名
+弹窗上方从左到右依次显示'均值'、'最大值'、'最小值'、'上行天数'四项指标
+四项指标均显示具体数值，单位为米（m）或天，无'--'或空白</t>
+  </si>
+  <si>
+    <t>点击对象: 杨庄行缩略图</t>
   </si>
   <si>
     <t>TP-CH1-008-002</t>
   </si>
   <si>
-    <t>验证水文数据表格功能弹窗上方正确显示均值最大值最小值上行天数统计指标</t>
-  </si>
-  <si>
-    <t>已弹出水位趋势弹窗</t>
-  </si>
-  <si>
-    <t>1. 观察弹窗上方区域
-2. 确认四个统计指标</t>
-  </si>
-  <si>
-    <t>显示均值数值
-显示最大值数值
-显示最小值数值
-显示上行天数</t>
+    <t>验证弹窗均值等于近七日有效水位之和除以有效天数</t>
+  </si>
+  <si>
+    <t>杨庄站近7日水位数据已知（测试前从数据库取数）</t>
+  </si>
+  <si>
+    <t>1. 从数据库查询杨庄站近7日的逐日水位值
+2. 手动计算均值：有效水位之和 ÷ 有效天数（保留2位小数）
+3. 点击杨庄行缩略图打开趋势弹窗
+4. 对比弹窗'均值'指标显示值与手动计算值</t>
+  </si>
+  <si>
+    <t>弹窗'均值'显示值与手动计算值一致（允许±0.01m舍入误差）
+均值为数值格式，保留2位小数
+存在缺测日时，分母为有效天数而非固定7</t>
+  </si>
+  <si>
+    <t>数据校验类：计算逻辑验证</t>
+  </si>
+  <si>
+    <t>杨庄站近7日水位（执行时从数据库获取）</t>
   </si>
   <si>
     <t>TP-CH1-008-003</t>
   </si>
   <si>
-    <t>验证水文数据表格功能弹窗下方正确显示七日水位折线图</t>
-  </si>
-  <si>
-    <t>1. 观察弹窗下方区域
-2. 确认折线图坐标轴</t>
-  </si>
-  <si>
-    <t>折线图横轴显示近七日日期
-折线图纵轴显示水位数值
-折线趋势与缩略图一致</t>
+    <t>验证弹窗折线图横轴为近七日日期纵轴为水位且走势与数据一致</t>
+  </si>
+  <si>
+    <t>已打开杨庄站趋势弹窗</t>
+  </si>
+  <si>
+    <t>1. 查看折线图横轴的刻度标签内容
+2. 查看折线图纵轴的刻度标签内容
+3. 将鼠标悬浮到折线图某一数据点上
+4. 对比悬浮提示值与数据库该日水位值</t>
+  </si>
+  <si>
+    <t>横轴显示近7个日期刻度（如08-09至08-15）
+纵轴显示水位数值刻度，单位为m
+悬浮提示显示具体日期与水位值（保留2位小数）
+悬浮提示水位值与数据库该日记录一致</t>
+  </si>
+  <si>
+    <t>验证站点: 杨庄</t>
   </si>
   <si>
     <t>TP-CH1-008-004</t>
   </si>
   <si>
-    <t>验证水文数据表格功能弹窗折线图涨跌颜色与缩略图一致</t>
-  </si>
-  <si>
-    <t>1. 观察折线图中上涨段颜色
-2. 观察折线图中下跌段颜色</t>
-  </si>
-  <si>
-    <t>折线图上涨段为绿色
-折线图下跌段为红色
-与缩略图颜色规则一致</t>
+    <t>验证弹窗最大值最小值与近七日实际数据一致</t>
+  </si>
+  <si>
+    <t>杨庄站近7日水位数据已知</t>
+  </si>
+  <si>
+    <t>1. 从数据库取杨庄站近7日水位，确定最大值与最小值
+2. 点击杨庄行缩略图打开弹窗
+3. 对比弹窗'最大值'指标与数据库最大值
+4. 对比弹窗'最小值'指标与数据库最小值</t>
+  </si>
+  <si>
+    <t>弹窗'最大值'等于近7日水位最高值（保留2位小数）
+弹窗'最小值'等于近7日水位最低值（保留2位小数）
+折线图最高点与最大值指标、最低点与最小值指标相互对应</t>
   </si>
   <si>
     <t>TP-CH1-008-005</t>
   </si>
   <si>
-    <t>验证水文数据表格功能水位趋势弹窗可正常关闭</t>
-  </si>
-  <si>
-    <t>1. 点击弹窗关闭按钮或遮罩层
-2. 观察弹窗是否关闭</t>
-  </si>
-  <si>
-    <t>弹窗正常关闭
-页面恢复到弹窗前状态</t>
+    <t>验证近七日缺测2天时上行天数统计仅基于有效相邻日计算</t>
+  </si>
+  <si>
+    <t>存在近7日中缺测2天的站点数据（由测试数据准备确认）</t>
+  </si>
+  <si>
+    <t>1. 从数据库取该站近7日水位，标记缺测日
+2. 手动统计有效相邻日对中水位上升的对数
+3. 点击该站缩略图打开弹窗
+4. 对比弹窗'上行天数'与手动统计值</t>
+  </si>
+  <si>
+    <t>'上行天数'等于手动统计的上升对数
+缺测日不参与上行天数计算（缺测日两侧的日对不计入）
+上行天数为整数，单位为'天'</t>
+  </si>
+  <si>
+    <t>缺测日数=2</t>
   </si>
   <si>
     <t>TP-CH1-008-006</t>
   </si>
   <si>
-    <t>验证水文数据表格功能不同站点弹出的趋势数据正确对应</t>
-  </si>
-  <si>
-    <t>数据测试</t>
-  </si>
-  <si>
-    <t>表格中有多个站点数据</t>
-  </si>
-  <si>
-    <t>1. 点击站点A的缩略图，记录弹窗数据
-2. 关闭弹窗
-3. 点击站点B的缩略图，记录弹窗数据
-4. 对比两个弹窗数据</t>
-  </si>
-  <si>
-    <t>站点A弹窗显示站点A的七日水位数据
-站点B弹窗显示站点B的七日水位数据
-两个弹窗数据不同且各自正确</t>
-  </si>
-  <si>
-    <t>数据测试：验证数据对应关系</t>
+    <t>验证点击弹窗关闭按钮或遮罩层后弹窗关闭且列表保持原状态</t>
+  </si>
+  <si>
+    <t>1. 点击弹窗右上角「×」关闭按钮
+2. 查看弹窗与遮罩层是否消失
+3. 再次打开弹窗后，点击遮罩层空白区域
+4. 查看列表表格数据与排序状态</t>
+  </si>
+  <si>
+    <t>点击「×」后弹窗与遮罩层均消失
+点击遮罩层空白区域弹窗同样关闭
+关闭弹窗后列表数据、排序状态、页码均保持不变</t>
   </si>
   <si>
     <t>TP-CH1-008-007</t>
   </si>
   <si>
-    <t>验证水文数据表格功能弹窗统计指标均值计算结果与七日水位数据一致</t>
-  </si>
-  <si>
-    <t>已知某站点近七日水位数据、已弹出该站点的水位趋势弹窗</t>
-  </si>
-  <si>
-    <t>1. 记录站点近七日水位数据
-2. 手动计算均值、最大值、最小值、上行天数
-3. 对比弹窗显示的统计指标</t>
-  </si>
-  <si>
-    <t>弹窗均值 = 七日水位数据平均值
-弹窗最大值 = 七日水位数据最大值
-弹窗最小值 = 七日水位数据最小值
-弹窗上行天数 = 水位比前一日高的天数</t>
-  </si>
-  <si>
-    <t>评审补充：数据校验测试点，验证统计指标计算正确性</t>
-  </si>
-  <si>
-    <t>示例：七日水位=[20,21,22,21,23,22,24]，均值=21.86，最大值=24，最小值=20，上行天数=4</t>
+    <t>验证快速连续点击不同缩略图时弹窗内容与最后点击对象一致</t>
+  </si>
+  <si>
+    <t>已查询出河道水情数据、列表至少包含杨庄、小浪底两个站点</t>
+  </si>
+  <si>
+    <t>1. 在1秒内快速依次点击'杨庄'行和'小浪底'行的「近七日水位变化」缩略图
+2. 等待弹窗渲染完成，查看页面上弹窗数量
+3. 查看弹窗标题中的站名与统计指标对应站点</t>
+  </si>
+  <si>
+    <t>页面上同一时刻仅存在一个趋势弹窗，无弹窗叠加
+弹窗标题与指标数据对应最后一次点击的站点（小浪底）
+弹窗加载过程无接口竞态导致的数据错乱（不出现杨庄的指标配小浪底的标题）</t>
+  </si>
+  <si>
+    <t>防重复打开/请求竞态场景（评审ISSUE-CH1-003补充）</t>
+  </si>
+  <si>
+    <t>点击序列: 杨庄→小浪底; 间隔&lt;500ms</t>
   </si>
   <si>
     <t>REQ-CH1-009</t>
   </si>
   <si>
-    <t>点击站名弹出同河流站点列表</t>
-  </si>
-  <si>
     <t>TP-CH1-009-001</t>
   </si>
   <si>
-    <t>验证水文数据表格功能站名显示为可点击的蓝色链接样式</t>
-  </si>
-  <si>
-    <t>河道水情Tab已加载</t>
-  </si>
-  <si>
-    <t>1. 观察表格站名列
-2. 确认站名样式</t>
-  </si>
-  <si>
-    <t>站名显示为蓝色文字
-鼠标悬停时显示手型光标
-站名可点击</t>
-  </si>
-  <si>
-    <t>UI测试：基于截图验证站名蓝色链接样式</t>
+    <t>验证河道水情点击杨庄站名弹出同河流站点列表且列头为四列</t>
+  </si>
+  <si>
+    <t>用户处于河道水情Tab、杨庄站名显示为蓝色链接样式</t>
+  </si>
+  <si>
+    <t>1. 点击'杨庄'站名链接
+2. 查看弹窗列头名称及顺序
+3. 查看弹窗数据行内容</t>
+  </si>
+  <si>
+    <t>弹窗列头从左到右依次为'省份'、'站名'、'水位'、'超警戒水位'四列
+弹窗数据行显示黄河上的站点列表
+弹窗标题含'黄河'或'同河流站点'字样</t>
+  </si>
+  <si>
+    <t>点击对象: 杨庄站名链接</t>
   </si>
   <si>
     <t>TP-CH1-009-002</t>
   </si>
   <si>
-    <t>验证水文数据表格功能点击站名弹出同河流站点列表弹窗</t>
-  </si>
-  <si>
-    <t>1. 点击站名'杨庄'（属于洪河）
-2. 观察弹窗内容</t>
-  </si>
-  <si>
-    <t>弹出站点列表弹窗
-弹窗仅显示洪河下的站点
-弹窗包含省份、站名、水位、超警戒水位列</t>
-  </si>
-  <si>
-    <t>站名=杨庄; 河流=洪河</t>
+    <t>验证站点弹窗中杨庄水位58.06与主列表数值一致</t>
+  </si>
+  <si>
+    <t>主列表已显示杨庄水位58.06、已打开杨庄站点弹窗</t>
+  </si>
+  <si>
+    <t>1. 记录主列表中'杨庄'行的水位与超警戒数值
+2. 点击'杨庄'站名打开弹窗
+3. 在弹窗中找到'杨庄'行，对比水位与超警戒数值</t>
+  </si>
+  <si>
+    <t>弹窗中杨庄水位显示58.06，与主列表一致
+弹窗中杨庄超警戒水位显示-91.94，与主列表一致
+弹窗中其他站点数值与数据库当日记录一致</t>
+  </si>
+  <si>
+    <t>数据一致性校验</t>
+  </si>
+  <si>
+    <t>杨庄水位=58.06; 超警戒=-91.94</t>
   </si>
   <si>
     <t>TP-CH1-009-003</t>
   </si>
   <si>
-    <t>验证水文数据表格功能河道水情站点弹窗列信息正确显示</t>
-  </si>
-  <si>
-    <t>已弹出河道水情站点列表弹窗</t>
-  </si>
-  <si>
-    <t>1. 观察弹窗表格列标题
-2. 确认列信息完整性</t>
-  </si>
-  <si>
-    <t>弹窗包含'省份'列
-弹窗包含'站名'列
-弹窗包含'水位'列
-弹窗包含'超警戒水位'列</t>
+    <t>验证点击黄河站点弹窗仅包含黄河站点不含其他河流</t>
+  </si>
+  <si>
+    <t>主列表同时存在黄河与伊洛河站点（如杨庄、伊洛河站）</t>
+  </si>
+  <si>
+    <t>1. 点击'杨庄'（黄河）站名打开弹窗
+2. 逐行查看弹窗中所有站名
+3. 关闭弹窗后点击'伊洛河'站站名，再次查看弹窗站点范围</t>
+  </si>
+  <si>
+    <t>杨庄弹窗中包含花园口、小浪底等黄河站点
+杨庄弹窗中不包含'伊洛河'站等非黄河站点
+伊洛河站弹窗仅包含伊洛河水系站点，不包含黄河站点</t>
+  </si>
+  <si>
+    <t>点击对象: 杨庄(黄河)、伊洛河站</t>
   </si>
   <si>
     <t>TP-CH1-009-004</t>
   </si>
   <si>
-    <t>验证水文数据表格功能水库水情站点弹窗列信息正确显示</t>
-  </si>
-  <si>
-    <t>切换到水库水情Tab、点击水库站名弹出弹窗</t>
-  </si>
-  <si>
-    <t>1. 切换到水库水情Tab
-2. 点击任意水库站名
-3. 观察弹窗表格列标题</t>
-  </si>
-  <si>
-    <t>弹窗包含'省份'列
-弹窗包含'库名'列
-弹窗包含'库水位'列
-弹窗包含'日变幅'列</t>
+    <t>验证站名弹窗关闭按钮可正常关闭弹窗</t>
+  </si>
+  <si>
+    <t>已打开杨庄站点弹窗</t>
+  </si>
+  <si>
+    <t>1. 点击弹窗右上角「×」关闭按钮
+2. 查看弹窗与遮罩层是否消失
+3. 查看主列表数据是否保持原状态</t>
+  </si>
+  <si>
+    <t>弹窗与遮罩层均消失
+主列表数据、页码、排序状态不变
+可再次点击站名重新打开弹窗</t>
   </si>
   <si>
     <t>TP-CH1-009-005</t>
   </si>
   <si>
-    <t>验证水文数据表格功能站点列表弹窗数据范围仅包含同河流站点</t>
-  </si>
-  <si>
-    <t>已弹出站点列表弹窗</t>
-  </si>
-  <si>
-    <t>1. 点击洪河的'杨庄'站名
-2. 检查弹窗中所有站点的河流归属</t>
-  </si>
-  <si>
-    <t>弹窗中所有站点均属于洪河
-不包含其他河流的站点</t>
-  </si>
-  <si>
-    <t>数据测试：验证数据范围正确性</t>
+    <t>验证水库水情点击库名弹窗列头为省份库名库水位日变幅四列</t>
+  </si>
+  <si>
+    <t>用户已切换到水库水情Tab、库名显示为蓝色链接样式</t>
+  </si>
+  <si>
+    <t>1. 点击任意水库的库名链接（如'小浪底'）
+2. 查看弹窗列头名称及顺序
+3. 查看弹窗数据行内容</t>
+  </si>
+  <si>
+    <t>弹窗列头从左到右依次为'省份'、'库名'、'库水位'、'日变幅'四列
+弹窗数据行显示同水库/同河流的水库数据
+'日变幅'列数值带正负号（如+0.15/-0.20）</t>
+  </si>
+  <si>
+    <t>点击对象: 水库库名链接</t>
+  </si>
+  <si>
+    <t>TP-CH1-009-006</t>
+  </si>
+  <si>
+    <t>验证水库弹窗日变幅等于当日库水位减前一日库水位</t>
+  </si>
+  <si>
+    <t>已知某水库当日与前一日库水位值（从数据库获取）</t>
+  </si>
+  <si>
+    <t>1. 从数据库取该水库当日库水位A与前一日库水位B
+2. 手动计算日变幅 = A - B（保留2位小数）
+3. 点击该水库库名打开弹窗
+4. 对比弹窗'日变幅'列数值与计算值</t>
+  </si>
+  <si>
+    <t>弹窗'日变幅'数值等于A-B的计算结果（允许±0.01m舍入误差）
+A&gt;B时日变幅显示正值（带+号或默认正数），A&lt;B时显示负值
+前一日无数据时日变幅显示'--'</t>
+  </si>
+  <si>
+    <t>日变幅=当日库水位-前一日库水位</t>
   </si>
   <si>
     <t>REQ-CH1-010</t>
   </si>
   <si>
-    <t>超警戒水位红色高亮与延迟标签</t>
-  </si>
-  <si>
     <t>TP-CH1-010-001</t>
   </si>
   <si>
-    <t>验证水文数据表格功能超警戒水位有数值时显示为红色高亮</t>
-  </si>
-  <si>
-    <t>存在超警戒水位有数值的站点数据</t>
-  </si>
-  <si>
-    <t>1. 找到超警戒水位有具体数值的行
-2. 观察该数值的显示颜色</t>
-  </si>
-  <si>
-    <t>超警戒水位数值以红色字体显示
-红色醒目易识别</t>
+    <t>验证龙羊峡水位225.30超警戒225.00时数值红色高亮显示</t>
+  </si>
+  <si>
+    <t>列表数据包含龙羊峡站（水位225.30，警戒水位225.00）</t>
+  </si>
+  <si>
+    <t>1. 在列表中找到'龙羊峡'行
+2. 查看该行'水位'列数值225.30的字体颜色
+3. 查看该行'超警戒'列数值0.30的显示
+4. 查看水位未超警戒的'杨庄'行水位58.06的字体颜色作为对照</t>
+  </si>
+  <si>
+    <t>龙羊峡行'水位'列数值225.30显示为红色字体
+该行'超警戒'列显示0.30（正值）
+杨庄行水位58.06为默认黑色字体，无红色高亮
+红色高亮仅作用于超警戒数值本身，不影响整行其他列</t>
+  </si>
+  <si>
+    <t>截图数据：龙羊峡为唯一超警戒站点</t>
+  </si>
+  <si>
+    <t>龙羊峡水位=225.30; 警戒=225.00; 超=0.30</t>
   </si>
   <si>
     <t>TP-CH1-010-002</t>
   </si>
   <si>
-    <t>验证水文数据表格功能超警戒水位为--时正常颜色显示非红色</t>
-  </si>
-  <si>
-    <t>存在超警戒水位为'--'的站点数据</t>
-  </si>
-  <si>
-    <t>1. 找到超警戒水位为'--'的行
-2. 观察显示颜色</t>
-  </si>
-  <si>
-    <t>'--'以正常颜色（非红色）显示</t>
-  </si>
-  <si>
-    <t>基于截图：当前所有行超警戒水位均为'--'，显示为正常颜色</t>
+    <t>验证水位等于警戒水位临界值时不显示红色高亮</t>
+  </si>
+  <si>
+    <t>构造测试数据：某站水位=警戒水位（如均为150.00）</t>
+  </si>
+  <si>
+    <t>1. 查询包含该临界值站点的列表数据
+2. 查看该站'水位'列数值150.00的字体颜色
+3. 查看该站'超警戒'列数值显示</t>
+  </si>
+  <si>
+    <t>水位=警戒水位（超警戒=0.00）时，水位数值为默认黑色，不显示红色
+'超警戒'列显示0.00
+仅水位&gt;警戒水位（超警戒&gt;0）时才触发红色高亮</t>
+  </si>
+  <si>
+    <t>临界值边界：等于警戒水位不算超警戒</t>
+  </si>
+  <si>
+    <t>水位=警戒水位=150.00; 超警戒=0.00</t>
   </si>
   <si>
     <t>TP-CH1-010-003</t>
   </si>
   <si>
-    <t>验证水文数据表格功能非当日更新数据行显示橙色延迟标签</t>
-  </si>
-  <si>
-    <t>存在非当日更新的数据</t>
-  </si>
-  <si>
-    <t>1. 找到时间非当日的行（如2026-07-21）
-2. 观察时间列显示</t>
-  </si>
-  <si>
-    <t>时间值右侧显示橙色'延迟'标签
-标签文字为'延迟'</t>
-  </si>
-  <si>
-    <t>基于截图：周堂桥行显示'2026-07-21 08:00 延迟'，橙色标签</t>
+    <t>验证站点弹窗中超警戒水位正值同样红色高亮</t>
+  </si>
+  <si>
+    <t>同河流站点中存在超警戒站点、已打开站点弹窗</t>
+  </si>
+  <si>
+    <t>1. 点击某站名打开同河流站点弹窗
+2. 找到'超警戒水位'列为正值的站点行
+3. 查看该数值字体颜色
+4. 查看超警戒为负值的站点行数值颜色作为对照</t>
+  </si>
+  <si>
+    <t>弹窗中超警戒水位为正值的数值显示红色字体
+超警戒水位为负值的数值显示默认黑色
+弹窗内高亮规则与主列表一致</t>
+  </si>
+  <si>
+    <t>验证对象: 站点弹窗超警戒水位列</t>
   </si>
   <si>
     <t>TP-CH1-010-004</t>
   </si>
   <si>
-    <t>验证水文数据表格功能当日更新数据行不显示延迟标签</t>
-  </si>
-  <si>
-    <t>存在当日更新的数据</t>
-  </si>
-  <si>
-    <t>1. 找到时间为当日的行（如2026-07-29）
-2. 观察时间列显示</t>
-  </si>
-  <si>
-    <t>时间值右侧不显示'延迟'标签
-仅显示时间值</t>
-  </si>
-  <si>
-    <t>基于截图：大部分行时间为2026-07-29，无延迟标签</t>
+    <t>验证超警戒水位排序后红色高亮仍跟随数值正确显示</t>
+  </si>
+  <si>
+    <t>列表含超警戒站点（龙羊峡）与非超警戒站点</t>
+  </si>
+  <si>
+    <t>1. 点击「水位」列表头执行降序排序
+2. 查看排序后龙羊峡行水位225.30的字体颜色
+3. 切换升序后再次查看该行颜色</t>
+  </si>
+  <si>
+    <t>排序后龙羊峡行无论处于哪一行，其水位225.30始终为红色
+非超警戒站点排序后仍为黑色
+排序切换过程中无红色高亮残留到错误行</t>
+  </si>
+  <si>
+    <t>排序列=水位</t>
   </si>
   <si>
     <t>TP-CH1-010-005</t>
   </si>
   <si>
-    <t>验证水文数据表格功能红色高亮和延迟标签可同时存在于同一行</t>
-  </si>
-  <si>
-    <t>存在非当日更新且超警戒水位有数值的站点</t>
-  </si>
-  <si>
-    <t>1. 构造或找到非当日更新且超警戒水位有数值的行
-2. 观察该行显示</t>
-  </si>
-  <si>
-    <t>超警戒水位数值显示为红色
-时间列显示延迟标签
-两个样式互不影响</t>
+    <t>验证查询日期早于站点更新日期时该行显示延迟标签</t>
+  </si>
+  <si>
+    <t>存在数据更新时间早于查询日期的站点（由测试数据准备确认）</t>
+  </si>
+  <si>
+    <t>1. 在「日期」选择器选择目标日期并点击「查询」
+2. 找到数据更新时间早于该日期的站点行
+3. 查看该行'时间'列附近的标签显示</t>
+  </si>
+  <si>
+    <t>该数据行显示'延迟'标签
+'延迟'标签位于时间值旁，样式为标签形式（有底色边框）
+标签文字为'延迟'二字，清晰可读</t>
+  </si>
+  <si>
+    <t>站点数据更新时间&lt;查询日期</t>
+  </si>
+  <si>
+    <t>TP-CH1-010-006</t>
+  </si>
+  <si>
+    <t>验证当日更新的数据行不显示延迟标签</t>
+  </si>
+  <si>
+    <t>存在查询日期当日更新的数据行</t>
+  </si>
+  <si>
+    <t>1. 查询当日更新数据的站点列表
+2. 找到数据更新时间等于查询日期的数据行
+3. 查看该行'时间'列附近是否有标签</t>
+  </si>
+  <si>
+    <t>当日更新的数据行时间值旁无'延迟'标签
+时间值为默认黑色字体
+列表中'延迟'标签仅出现在非当日更新的行</t>
+  </si>
+  <si>
+    <t>站点数据更新时间=查询日期</t>
+  </si>
+  <si>
+    <t>TP-CH1-010-007</t>
+  </si>
+  <si>
+    <t>验证延迟标签在排序和翻页后仍保留在对应数据行</t>
+  </si>
+  <si>
+    <t>列表存在带'延迟'标签的数据行</t>
+  </si>
+  <si>
+    <t>1. 记录带'延迟'标签的站名
+2. 点击「水位」列表头排序，查找该站所在行的标签
+3. 翻页后再返回，再次查找该站所在行的标签</t>
+  </si>
+  <si>
+    <t>排序后该站所在行仍显示'延迟'标签
+翻页返回后标签不丢失
+无'延迟'标签的行在排序翻页后不被错误添加标签</t>
+  </si>
+  <si>
+    <t>验证对象: 带延迟标签的行</t>
+  </si>
+  <si>
+    <t>REQ-CH1-011</t>
+  </si>
+  <si>
+    <t>TP-CH1-011-001</t>
+  </si>
+  <si>
+    <t>验证点击导出按钮按当前筛选条件导出文件且内容与列表一致</t>
+  </si>
+  <si>
+    <t>已设置筛选条件：日期=2026-08-15、省份=河南、流域=黄河流域、河名=黄河、已点击查询显示10条结果</t>
+  </si>
+  <si>
+    <t>1. 点击「导出」按钮
+2. 等待导出文件下载完成并打开
+3. 对比导出文件的列字段与表格列头
+4. 对比导出数据行数与列表总条数</t>
+  </si>
+  <si>
+    <t>浏览器成功下载导出文件（Excel/CSV格式）
+导出文件字段包含时间、行政区划、站名、水位、警戒水位等表格列
+导出数据行数为10行，与筛选后总条数一致
+导出数据中杨庄行水位为58.06，与页面显示一致</t>
+  </si>
+  <si>
+    <t>导出按钮来自截图识别</t>
+  </si>
+  <si>
+    <t>筛选条件: 河南/黄河流域/黄河/2026-08-15; 预期行数=10</t>
+  </si>
+  <si>
+    <t>TP-CH1-011-002</t>
+  </si>
+  <si>
+    <t>验证筛选结果为空时点击导出给出明确提示且不生成空文件</t>
+  </si>
+  <si>
+    <t>已通过站名关键字查询构造出0条结果的筛选条件</t>
+  </si>
+  <si>
+    <t>1. 在「站名关键字」输入'不存在的站名XYZ'并点击「查询」
+2. 确认表格显示'暂无数据'
+3. 点击「导出」按钮
+4. 查看页面提示信息与浏览器下载行为</t>
+  </si>
+  <si>
+    <t>页面显示'暂无数据可导出'类明确提示（Toast或弹窗）
+浏览器不下载空文件或仅含表头的文件
+页面无JS报错或接口500错误</t>
+  </si>
+  <si>
+    <t>站名关键字=不存在的站名XYZ; 结果=0条</t>
+  </si>
+  <si>
+    <t>TP-CH1-011-003</t>
+  </si>
+  <si>
+    <t>验证站名关键字输入脚本字符查询不被执行且页面无弹窗</t>
+  </si>
+  <si>
+    <t>1. 在「站名关键字」输入框输入'&lt;script&gt;alert(1)&lt;/script&gt;'
+2. 点击「查询」按钮
+3. 观察浏览器是否弹出alert对话框
+4. 查看表格区域与浏览器控制台的响应</t>
+  </si>
+  <si>
+    <t>浏览器不弹出alert(1)对话框（XSS未执行）
+输入内容作为普通文本参与查询或显示
+表格显示'暂无数据'或无匹配结果，页面不报错</t>
+  </si>
+  <si>
+    <t>安全测试：XSS注入验证</t>
+  </si>
+  <si>
+    <t>输入值=&lt;script&gt;alert(1)&lt;/script&gt;</t>
   </si>
 </sst>
 </file>
@@ -1175,11 +1452,10 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -1336,13 +1612,13 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F4E79"/>
-        <bgColor rgb="FF1F4E79"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD6E4F0"/>
-        <bgColor rgb="FFD6E4F0"/>
+        <fgColor rgb="FFDDEBF7"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -1542,16 +1818,16 @@
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color rgb="FF999999"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color rgb="FF999999"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
+        <color rgb="FF999999"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color rgb="FF999999"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1656,19 +1932,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1677,7 +1953,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1801,22 +2077,18 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2163,170 +2435,226 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="2" width="20" customWidth="1"/>
+    <col min="1" max="1" width="40" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" spans="1:2">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" ht="16.5" spans="1:2">
-      <c r="A2" s="5" t="s">
+    <row r="2" ht="15" spans="1:2">
+      <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="5">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" ht="16.5" spans="1:2">
-      <c r="A3" s="6" t="s">
+      <c r="B2" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="6" t="s">
+    </row>
+    <row r="3" ht="15" spans="1:2">
+      <c r="A3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" ht="15" spans="1:2">
+      <c r="A4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" ht="15" spans="1:2">
+      <c r="A5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" ht="15" spans="1:1">
+      <c r="A7" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" ht="15" spans="1:1">
+      <c r="A12" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16">
         <v>3</v>
       </c>
     </row>
-    <row r="4" ht="16.5" spans="1:2">
-      <c r="A4" s="5" t="s">
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" ht="15" spans="1:1">
+      <c r="A20" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24">
         <v>4</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" ht="16.5" spans="1:2">
-      <c r="A5" s="6" t="s">
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25">
         <v>5</v>
       </c>
-      <c r="B5" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" ht="16.5" spans="1:2">
-      <c r="A6" s="5" t="s">
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
+        <v>29</v>
+      </c>
+      <c r="B29">
         <v>6</v>
       </c>
-      <c r="B6" s="5">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" ht="16.5" spans="1:2">
-      <c r="A7" s="6" t="s">
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>30</v>
+      </c>
+      <c r="B30">
         <v>7</v>
       </c>
-      <c r="B7" s="6">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" ht="16.5" spans="1:2">
-      <c r="A8" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" ht="16.5" spans="1:2">
-      <c r="A9" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" ht="16.5" spans="1:2">
-      <c r="A10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" ht="16.5" spans="1:2">
-      <c r="A11" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="6">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="12" ht="16.5" spans="1:2">
-      <c r="A12" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" ht="16.5" spans="1:2">
-      <c r="A13" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B13" s="6">
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
+        <v>31</v>
+      </c>
+      <c r="B31">
         <v>2</v>
-      </c>
-    </row>
-    <row r="14" ht="16.5" spans="1:2">
-      <c r="A14" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" s="5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" ht="16.5" spans="1:2">
-      <c r="A15" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" ht="16.5" spans="1:2">
-      <c r="A16" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" ht="16.5" spans="1:2">
-      <c r="A17" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" ht="16.5" spans="1:2">
-      <c r="A18" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B18" s="5">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="19" ht="16.5" spans="1:2">
-      <c r="A19" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" ht="16.5" spans="1:2">
-      <c r="A20" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -2338,2266 +2666,2355 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N51"/>
+  <dimension ref="A1:N53"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="45" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="1" max="1" width="13" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="4" max="4" width="40" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="10" customWidth="1"/>
-    <col min="7" max="7" width="25" customWidth="1"/>
-    <col min="8" max="8" width="40" customWidth="1"/>
-    <col min="9" max="9" width="35" customWidth="1"/>
-    <col min="10" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="10" customWidth="1"/>
-    <col min="12" max="12" width="18" customWidth="1"/>
-    <col min="13" max="13" width="25" customWidth="1"/>
-    <col min="14" max="14" width="10" customWidth="1"/>
+    <col min="7" max="7" width="26" customWidth="1"/>
+    <col min="8" max="8" width="50" customWidth="1"/>
+    <col min="9" max="9" width="55" customWidth="1"/>
+    <col min="10" max="10" width="26" customWidth="1"/>
+    <col min="11" max="11" width="8" customWidth="1"/>
+    <col min="12" max="12" width="14" customWidth="1"/>
+    <col min="13" max="13" width="30" customWidth="1"/>
+    <col min="14" max="14" width="9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1" spans="1:14">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" ht="60" customHeight="1" spans="1:14">
       <c r="A2" s="2" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" ht="60" customHeight="1" spans="1:14">
       <c r="A3" s="3" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>3</v>
+        <v>63</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" ht="60" customHeight="1" spans="1:14">
       <c r="A4" s="2" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>3</v>
+        <v>71</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1" spans="1:14">
       <c r="A5" s="3" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" ht="60" customHeight="1" spans="1:14">
       <c r="A6" s="2" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>3</v>
+        <v>82</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1" spans="1:14">
       <c r="A7" s="3" t="s">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>47</v>
+        <v>86</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>3</v>
+        <v>90</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1" spans="1:14">
       <c r="A8" s="2" t="s">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>75</v>
+        <v>14</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>47</v>
+        <v>93</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>3</v>
+        <v>96</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" ht="60" customHeight="1" spans="1:14">
       <c r="A9" s="3" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>80</v>
+        <v>23</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" ht="60" customHeight="1" spans="1:14">
       <c r="A10" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>80</v>
+        <v>23</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>47</v>
+        <v>104</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>3</v>
+        <v>107</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" ht="60" customHeight="1" spans="1:14">
       <c r="A11" s="3" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>80</v>
+        <v>23</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>47</v>
+        <v>111</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>3</v>
+        <v>114</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12" ht="60" customHeight="1" spans="1:14">
       <c r="A12" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>80</v>
+        <v>23</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>47</v>
+        <v>117</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>3</v>
+        <v>120</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" ht="60" customHeight="1" spans="1:14">
       <c r="A13" s="3" t="s">
-        <v>79</v>
+        <v>122</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>80</v>
+        <v>24</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>102</v>
+        <v>123</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>103</v>
+        <v>124</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>47</v>
+        <v>125</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>106</v>
+        <v>128</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14" ht="60" customHeight="1" spans="1:14">
       <c r="A14" s="2" t="s">
-        <v>79</v>
+        <v>122</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>80</v>
+        <v>24</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>107</v>
+        <v>129</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>75</v>
+        <v>14</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>47</v>
+        <v>131</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>111</v>
+        <v>70</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15" ht="60" customHeight="1" spans="1:14">
       <c r="A15" s="3" t="s">
-        <v>79</v>
+        <v>122</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>80</v>
+        <v>24</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>112</v>
+        <v>134</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>113</v>
+        <v>135</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>114</v>
+        <v>136</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>115</v>
+        <v>137</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>3</v>
+        <v>139</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>3</v>
+        <v>140</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16" ht="60" customHeight="1" spans="1:14">
       <c r="A16" s="2" t="s">
-        <v>79</v>
+        <v>122</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>80</v>
+        <v>24</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>117</v>
+        <v>141</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>118</v>
+        <v>142</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>119</v>
+        <v>143</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>120</v>
+        <v>144</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>122</v>
+        <v>146</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>87</v>
+        <v>147</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="17" ht="60" customHeight="1" spans="1:14">
       <c r="A17" s="3" t="s">
-        <v>123</v>
+        <v>148</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>124</v>
+        <v>25</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>125</v>
+        <v>149</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>126</v>
+        <v>150</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>47</v>
+        <v>151</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>127</v>
+        <v>152</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>128</v>
+        <v>153</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>3</v>
+        <v>154</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>87</v>
+        <v>155</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18" ht="60" customHeight="1" spans="1:14">
       <c r="A18" s="2" t="s">
-        <v>123</v>
+        <v>148</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>124</v>
+        <v>25</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>129</v>
+        <v>156</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>130</v>
+        <v>157</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>47</v>
+        <v>158</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>131</v>
+        <v>159</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>132</v>
+        <v>160</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>133</v>
+        <v>161</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19" ht="60" customHeight="1" spans="1:14">
       <c r="A19" s="3" t="s">
-        <v>123</v>
+        <v>148</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>124</v>
+        <v>25</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>134</v>
+        <v>162</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>138</v>
+        <v>166</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>3</v>
+        <v>167</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="20" ht="60" customHeight="1" spans="1:14">
       <c r="A20" s="2" t="s">
-        <v>123</v>
+        <v>148</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>124</v>
+        <v>25</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>139</v>
+        <v>168</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>140</v>
+        <v>169</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>141</v>
+        <v>170</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>142</v>
+        <v>171</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>143</v>
+        <v>172</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>3</v>
+        <v>173</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="21" ht="60" customHeight="1" spans="1:14">
       <c r="A21" s="3" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>145</v>
+        <v>25</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>146</v>
+        <v>174</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>147</v>
+        <v>175</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>148</v>
+        <v>176</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>149</v>
+        <v>177</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>150</v>
+        <v>178</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>3</v>
+        <v>179</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="22" ht="60" customHeight="1" spans="1:14">
       <c r="A22" s="2" t="s">
-        <v>144</v>
+        <v>180</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>145</v>
+        <v>26</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>151</v>
+        <v>181</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>152</v>
+        <v>182</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>153</v>
+        <v>183</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>154</v>
+        <v>184</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>155</v>
+        <v>185</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>3</v>
+        <v>186</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>3</v>
+        <v>187</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="23" ht="60" customHeight="1" spans="1:14">
       <c r="A23" s="3" t="s">
-        <v>144</v>
+        <v>180</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>145</v>
+        <v>26</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>156</v>
+        <v>188</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>157</v>
+        <v>189</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>158</v>
+        <v>190</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>159</v>
+        <v>191</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>160</v>
+        <v>192</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>3</v>
+        <v>193</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="24" ht="60" customHeight="1" spans="1:14">
       <c r="A24" s="2" t="s">
-        <v>144</v>
+        <v>180</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>145</v>
+        <v>26</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>161</v>
+        <v>194</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>162</v>
+        <v>195</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>69</v>
+        <v>15</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>148</v>
+        <v>196</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>163</v>
+        <v>197</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>164</v>
+        <v>198</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>165</v>
+        <v>199</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>3</v>
+        <v>200</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="25" ht="60" customHeight="1" spans="1:14">
       <c r="A25" s="3" t="s">
-        <v>144</v>
+        <v>180</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>145</v>
+        <v>26</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>166</v>
+        <v>201</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>167</v>
+        <v>202</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>168</v>
+        <v>203</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>169</v>
+        <v>204</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>170</v>
+        <v>205</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>3</v>
+        <v>206</v>
       </c>
       <c r="N25" s="3" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="26" ht="60" customHeight="1" spans="1:14">
       <c r="A26" s="2" t="s">
-        <v>171</v>
+        <v>207</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>172</v>
+        <v>27</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>173</v>
+        <v>208</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>174</v>
+        <v>209</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>176</v>
+        <v>211</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>177</v>
+        <v>212</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>3</v>
+        <v>213</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="27" ht="60" customHeight="1" spans="1:14">
       <c r="A27" s="3" t="s">
-        <v>171</v>
+        <v>207</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>172</v>
+        <v>27</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>178</v>
+        <v>214</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>179</v>
+        <v>215</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>180</v>
+        <v>216</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>181</v>
+        <v>217</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>182</v>
+        <v>218</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>3</v>
+        <v>219</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>183</v>
+        <v>220</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="28" ht="60" customHeight="1" spans="1:14">
       <c r="A28" s="2" t="s">
-        <v>171</v>
+        <v>207</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>172</v>
+        <v>27</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>184</v>
+        <v>221</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>185</v>
+        <v>222</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>186</v>
+        <v>223</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>187</v>
+        <v>224</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>188</v>
+        <v>225</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>3</v>
+        <v>146</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>3</v>
+        <v>226</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="29" ht="60" customHeight="1" spans="1:14">
       <c r="A29" s="3" t="s">
-        <v>171</v>
+        <v>207</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>172</v>
+        <v>27</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>189</v>
+        <v>227</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>190</v>
+        <v>228</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>180</v>
+        <v>229</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>191</v>
+        <v>230</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>192</v>
+        <v>231</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>3</v>
+        <v>232</v>
       </c>
       <c r="N29" s="3" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="30" ht="60" customHeight="1" spans="1:14">
       <c r="A30" s="2" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>194</v>
+        <v>27</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>195</v>
+        <v>233</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>196</v>
+        <v>234</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>69</v>
+        <v>17</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>197</v>
+        <v>235</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>199</v>
+        <v>237</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>200</v>
+        <v>70</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>3</v>
+        <v>63</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="31" ht="60" customHeight="1" spans="1:14">
       <c r="A31" s="3" t="s">
-        <v>193</v>
+        <v>238</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>194</v>
+        <v>28</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>201</v>
+        <v>239</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>202</v>
+        <v>240</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>203</v>
+        <v>241</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>204</v>
+        <v>242</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>205</v>
+        <v>243</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>206</v>
+        <v>70</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="M31" s="3" t="s">
-        <v>3</v>
+        <v>244</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="32" ht="60" customHeight="1" spans="1:14">
       <c r="A32" s="2" t="s">
-        <v>193</v>
+        <v>238</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>194</v>
+        <v>28</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>207</v>
+        <v>245</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>208</v>
+        <v>246</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>209</v>
+        <v>247</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>210</v>
+        <v>248</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>211</v>
+        <v>249</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>212</v>
+        <v>250</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>3</v>
+        <v>251</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="33" ht="60" customHeight="1" spans="1:14">
       <c r="A33" s="3" t="s">
-        <v>193</v>
+        <v>238</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>194</v>
+        <v>28</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>213</v>
+        <v>252</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>214</v>
+        <v>253</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>215</v>
+        <v>254</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>216</v>
+        <v>255</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>217</v>
+        <v>256</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>3</v>
+        <v>257</v>
       </c>
       <c r="N33" s="3" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="34" ht="60" customHeight="1" spans="1:14">
       <c r="A34" s="2" t="s">
-        <v>193</v>
+        <v>238</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>194</v>
+        <v>28</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>218</v>
+        <v>258</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>219</v>
+        <v>259</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>220</v>
+        <v>260</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>221</v>
+        <v>261</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>222</v>
+        <v>262</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>3</v>
+        <v>257</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="35" ht="60" customHeight="1" spans="1:14">
       <c r="A35" s="3" t="s">
-        <v>223</v>
+        <v>238</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>224</v>
+        <v>28</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>225</v>
+        <v>263</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>226</v>
+        <v>264</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>227</v>
+        <v>265</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>228</v>
+        <v>266</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>229</v>
+        <v>267</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>3</v>
+        <v>146</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="L35" s="3" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="M35" s="3" t="s">
-        <v>3</v>
+        <v>268</v>
       </c>
       <c r="N35" s="3" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="36" ht="60" customHeight="1" spans="1:14">
       <c r="A36" s="2" t="s">
-        <v>223</v>
+        <v>238</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>224</v>
+        <v>28</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>230</v>
+        <v>269</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>231</v>
+        <v>270</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>232</v>
+        <v>254</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>233</v>
+        <v>271</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>234</v>
+        <v>272</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="37" ht="60" customHeight="1" spans="1:14">
       <c r="A37" s="3" t="s">
-        <v>223</v>
+        <v>238</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>224</v>
+        <v>28</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>235</v>
+        <v>273</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>236</v>
+        <v>274</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>232</v>
+        <v>275</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>237</v>
+        <v>276</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>238</v>
+        <v>277</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>3</v>
+        <v>278</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="L37" s="3" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="M37" s="3" t="s">
-        <v>3</v>
+        <v>279</v>
       </c>
       <c r="N37" s="3" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="38" ht="60" customHeight="1" spans="1:14">
       <c r="A38" s="2" t="s">
-        <v>223</v>
+        <v>280</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>224</v>
+        <v>29</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>239</v>
+        <v>281</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>240</v>
+        <v>282</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>232</v>
+        <v>283</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>241</v>
+        <v>284</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>242</v>
+        <v>285</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>3</v>
+        <v>286</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="39" ht="60" customHeight="1" spans="1:14">
       <c r="A39" s="3" t="s">
-        <v>223</v>
+        <v>280</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>224</v>
+        <v>29</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>243</v>
+        <v>287</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>244</v>
+        <v>288</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>232</v>
+        <v>289</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>245</v>
+        <v>290</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>246</v>
+        <v>291</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>3</v>
+        <v>292</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="L39" s="3" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="M39" s="3" t="s">
-        <v>3</v>
+        <v>293</v>
       </c>
       <c r="N39" s="3" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="40" ht="60" customHeight="1" spans="1:14">
       <c r="A40" s="2" t="s">
-        <v>223</v>
+        <v>280</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>224</v>
+        <v>29</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>247</v>
+        <v>294</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>248</v>
+        <v>295</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>249</v>
+        <v>14</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>250</v>
+        <v>296</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>251</v>
+        <v>297</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>252</v>
+        <v>298</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>253</v>
+        <v>70</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>3</v>
+        <v>299</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="41" ht="60" customHeight="1" spans="1:14">
       <c r="A41" s="3" t="s">
-        <v>223</v>
+        <v>280</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>224</v>
+        <v>29</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>254</v>
+        <v>300</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>255</v>
+        <v>301</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>249</v>
+        <v>14</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>256</v>
+        <v>302</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>257</v>
+        <v>303</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>258</v>
+        <v>304</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>259</v>
+        <v>70</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="L41" s="3" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="M41" s="3" t="s">
-        <v>260</v>
+        <v>70</v>
       </c>
       <c r="N41" s="3" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="42" ht="60" customHeight="1" spans="1:14">
       <c r="A42" s="2" t="s">
-        <v>261</v>
+        <v>280</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>262</v>
+        <v>29</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>263</v>
+        <v>305</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>264</v>
+        <v>306</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>265</v>
+        <v>307</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>266</v>
+        <v>308</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>267</v>
+        <v>309</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>268</v>
+        <v>70</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>3</v>
+        <v>310</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="43" ht="60" customHeight="1" spans="1:14">
       <c r="A43" s="3" t="s">
-        <v>261</v>
+        <v>280</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>262</v>
+        <v>29</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>269</v>
+        <v>311</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>270</v>
+        <v>312</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>265</v>
+        <v>313</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>271</v>
+        <v>314</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>272</v>
+        <v>315</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>3</v>
+        <v>250</v>
       </c>
       <c r="K43" s="3" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="L43" s="3" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="M43" s="3" t="s">
-        <v>273</v>
+        <v>316</v>
       </c>
       <c r="N43" s="3" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="44" ht="60" customHeight="1" spans="1:14">
       <c r="A44" s="2" t="s">
-        <v>261</v>
+        <v>317</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>262</v>
+        <v>30</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>274</v>
+        <v>318</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>275</v>
+        <v>319</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>276</v>
+        <v>320</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>277</v>
+        <v>321</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>278</v>
+        <v>322</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>3</v>
+        <v>323</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>3</v>
+        <v>324</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="45" ht="60" customHeight="1" spans="1:14">
       <c r="A45" s="3" t="s">
-        <v>261</v>
+        <v>317</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>262</v>
+        <v>30</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>279</v>
+        <v>325</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>280</v>
+        <v>326</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>281</v>
+        <v>327</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>282</v>
+        <v>328</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>283</v>
+        <v>329</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>3</v>
+        <v>330</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="L45" s="3" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="M45" s="3" t="s">
-        <v>3</v>
+        <v>331</v>
       </c>
       <c r="N45" s="3" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="46" ht="60" customHeight="1" spans="1:14">
       <c r="A46" s="2" t="s">
-        <v>261</v>
+        <v>317</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>262</v>
+        <v>30</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>284</v>
+        <v>332</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>285</v>
+        <v>333</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>249</v>
+        <v>14</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>286</v>
+        <v>334</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>287</v>
+        <v>335</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>288</v>
+        <v>336</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>289</v>
+        <v>70</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>3</v>
+        <v>337</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="47" ht="60" customHeight="1" spans="1:14">
       <c r="A47" s="3" t="s">
-        <v>290</v>
+        <v>317</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>291</v>
+        <v>30</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>292</v>
+        <v>338</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>293</v>
+        <v>339</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>294</v>
+        <v>340</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>295</v>
+        <v>341</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>296</v>
+        <v>342</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="K47" s="3" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="L47" s="3" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>3</v>
+        <v>343</v>
       </c>
       <c r="N47" s="3" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="48" ht="60" customHeight="1" spans="1:14">
       <c r="A48" s="2" t="s">
-        <v>290</v>
+        <v>317</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>291</v>
+        <v>30</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>297</v>
+        <v>344</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>298</v>
+        <v>345</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>300</v>
+        <v>347</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>301</v>
+        <v>348</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>302</v>
+        <v>70</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>3</v>
+        <v>349</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="49" ht="60" customHeight="1" spans="1:14">
       <c r="A49" s="3" t="s">
-        <v>290</v>
+        <v>317</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>291</v>
+        <v>30</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>303</v>
+        <v>350</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>304</v>
+        <v>351</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>305</v>
+        <v>352</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>306</v>
+        <v>353</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>307</v>
+        <v>354</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>308</v>
+        <v>70</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="L49" s="3" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>3</v>
+        <v>355</v>
       </c>
       <c r="N49" s="3" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="50" ht="60" customHeight="1" spans="1:14">
       <c r="A50" s="2" t="s">
-        <v>290</v>
+        <v>317</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>291</v>
+        <v>30</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>309</v>
+        <v>356</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>310</v>
+        <v>357</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>311</v>
+        <v>358</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>312</v>
+        <v>359</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>313</v>
+        <v>360</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>314</v>
+        <v>70</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>3</v>
+        <v>361</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="51" ht="60" customHeight="1" spans="1:14">
       <c r="A51" s="3" t="s">
-        <v>290</v>
+        <v>362</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>291</v>
+        <v>31</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>315</v>
+        <v>363</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>316</v>
+        <v>364</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>317</v>
+        <v>365</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>318</v>
+        <v>366</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>319</v>
+        <v>367</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>3</v>
+        <v>368</v>
       </c>
       <c r="K51" s="3" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="L51" s="3" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="M51" s="3" t="s">
-        <v>3</v>
+        <v>369</v>
       </c>
       <c r="N51" s="3" t="s">
-        <v>44</v>
+        <v>56</v>
+      </c>
+    </row>
+    <row r="52" ht="60" customHeight="1" spans="1:14">
+      <c r="A52" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="J52" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="K52" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="L52" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="M52" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="N52" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="53" ht="60" customHeight="1" spans="1:14">
+      <c r="A53" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="I53" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="J53" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="K53" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="L53" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="M53" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="N53" s="3" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/.qoder/output/aiAutoTester/水文数据展示/06_testcase_export/水文数据展示_测试用例_20260818_v2.xlsx
+++ b/.qoder/output/aiAutoTester/水文数据展示/06_testcase_export/水文数据展示_测试用例_20260818_v2.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22185" windowHeight="9015" activeTab="1"/>
+    <workbookView windowWidth="27945" windowHeight="12255" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="统计汇总" sheetId="1" r:id="rId1"/>
@@ -338,7 +338,7 @@
     <t>TP-CH1-003-002</t>
   </si>
   <si>
-    <t>验证站名关键字'杨'模糊查询仅返回站名包含杨的站点</t>
+    <t>验证站名关键字模糊查询仅返回站名包含关键字的站点</t>
   </si>
   <si>
     <t>用户已进入河道水情Tab、系统存在站名'杨庄'的数据</t>
@@ -382,7 +382,7 @@
     <t>TP-CH1-003-004</t>
   </si>
   <si>
-    <t>验证日期选择未来日期'2026-08-19'查询后表格显示暂无数据</t>
+    <t>验证日期选择未来日期查询后表格显示暂无数据</t>
   </si>
   <si>
     <t>当前系统日期为2026-08-18、用户已进入河道水情Tab</t>
@@ -407,7 +407,7 @@
     <t>TP-CH1-003-005</t>
   </si>
   <si>
-    <t>验证仅选择省份'河南'不选其他条件时查询返回该省全部站点</t>
+    <t>验证仅选择省份不选其他条件时查询返回该省全部站点</t>
   </si>
   <si>
     <t>用户已进入河道水情Tab</t>
@@ -430,7 +430,7 @@
     <t>TP-CH1-003-006</t>
   </si>
   <si>
-    <t>验证1秒内快速连点查询按钮5次仅执行一次查询且无重复数据</t>
+    <t>验证快速连点查询按钮仅执行一次查询且无重复数据</t>
   </si>
   <si>
     <t>用户已进入河道水情Tab、浏览器开发者工具已打开Network面板</t>
@@ -459,7 +459,7 @@
     <t>TP-CH1-004-001</t>
   </si>
   <si>
-    <t>验证选择省份河南后流域下拉框联动加载黄河流域淮河等选项</t>
+    <t>验证选择省份后流域下拉框联动加载对应流域选项</t>
   </si>
   <si>
     <t>用户已进入河道水情Tab、筛选区所有控件为空</t>
@@ -503,7 +503,7 @@
     <t>TP-CH1-004-003</t>
   </si>
   <si>
-    <t>验证选择河南+黄河流域后河名下拉框联动加载黄河选项</t>
+    <t>验证选择省份和流域后河名下拉框联动加载对应河流选项</t>
   </si>
   <si>
     <t>筛选区所有控件为空、用户已进入河道水情Tab</t>
@@ -677,7 +677,7 @@
     <t>TP-CH1-006-001</t>
   </si>
   <si>
-    <t>验证分页器默认显示20条每页且总条数为10</t>
+    <t>验证分页器默认每页条数与总条数显示</t>
   </si>
   <si>
     <t>已查询出河南黄河10条数据</t>
@@ -702,7 +702,7 @@
     <t>TP-CH1-006-002</t>
   </si>
   <si>
-    <t>验证切换每页条数为50后表格刷新且分页信息同步更新</t>
+    <t>验证切换每页条数后表格刷新且分页信息同步更新</t>
   </si>
   <si>
     <t>已查询出列表数据、当前每页条数为20</t>
@@ -725,7 +725,7 @@
     <t>TP-CH1-006-003</t>
   </si>
   <si>
-    <t>验证数据量10条小于每页20条时仅显示一页且翻页按钮不可点击</t>
+    <t>验证数据量不足一页时仅显示一页且翻页按钮不可点击</t>
   </si>
   <si>
     <t>查询结果总条数为10、每页条数为20</t>
@@ -750,7 +750,7 @@
     <t>TP-CH1-006-004</t>
   </si>
   <si>
-    <t>验证数据超过每页条数时点击第2页加载后续数据</t>
+    <t>验证数据超过每页条数时点击下一页加载后续数据</t>
   </si>
   <si>
     <t>查询结果总条数大于20条</t>
@@ -981,7 +981,7 @@
     <t>TP-CH1-008-005</t>
   </si>
   <si>
-    <t>验证近七日缺测2天时上行天数统计仅基于有效相邻日计算</t>
+    <t>验证近七日存在缺测时上行天数统计仅基于有效相邻日计算</t>
   </si>
   <si>
     <t>存在近7日中缺测2天的站点数据（由测试数据准备确认）</t>
@@ -1071,7 +1071,7 @@
     <t>TP-CH1-009-002</t>
   </si>
   <si>
-    <t>验证站点弹窗中杨庄水位58.06与主列表数值一致</t>
+    <t>验证站点弹窗中杨庄水位与主列表数值一致</t>
   </si>
   <si>
     <t>主列表已显示杨庄水位58.06、已打开杨庄站点弹窗</t>
@@ -1185,7 +1185,7 @@
     <t>TP-CH1-010-001</t>
   </si>
   <si>
-    <t>验证龙羊峡水位225.30超警戒225.00时数值红色高亮显示</t>
+    <t>验证龙羊峡水位超警戒时数值红色高亮显示</t>
   </si>
   <si>
     <t>列表数据包含龙羊峡站（水位225.30，警戒水位225.00）</t>
@@ -1932,148 +1932,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="7">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2442,7 +2442,7 @@
     <col min="2" max="2" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" spans="1:2">
+    <row r="1" ht="15" customHeight="1" spans="1:2">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2450,7 +2450,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" ht="15" spans="1:2">
+    <row r="2" ht="15" customHeight="1" spans="1:2">
       <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
@@ -2458,7 +2458,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" ht="15" spans="1:2">
+    <row r="3" ht="15" customHeight="1" spans="1:2">
       <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
@@ -2466,7 +2466,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" ht="15" spans="1:2">
+    <row r="4" ht="15" customHeight="1" spans="1:2">
       <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
@@ -2474,7 +2474,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="5" ht="15" spans="1:2">
+    <row r="5" ht="15" customHeight="1" spans="1:2">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
@@ -2482,7 +2482,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" ht="15" spans="1:1">
+    <row r="7" ht="15" customHeight="1" spans="1:1">
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
@@ -2511,7 +2511,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" ht="15" spans="1:1">
+    <row r="12" ht="15" customHeight="1" spans="1:1">
       <c r="A12" s="4" t="s">
         <v>13</v>
       </c>
@@ -2564,7 +2564,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" ht="15" spans="1:1">
+    <row r="20" ht="15" customHeight="1" spans="1:1">
       <c r="A20" s="4" t="s">
         <v>20</v>
       </c>
